--- a/research/traditional_assets/database/data/italy/italy_transportation_railroads.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_transportation_railroads.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08165397723801457</v>
+        <v>0.08149220769264331</v>
       </c>
       <c r="C2">
-        <v>1391.462273353867</v>
+        <v>1379.492692510024</v>
       </c>
       <c r="D2">
-        <v>945.6622733538666</v>
+        <v>947.4656925100235</v>
       </c>
       <c r="E2">
-        <v>-1181.4</v>
+        <v>-1167.627</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.773</v>
       </c>
       <c r="G2">
         <v>445.8</v>
@@ -1451,28 +1451,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6927819000000001</v>
       </c>
       <c r="N2">
-        <v>122.7444444444444</v>
+        <v>122.0516625444444</v>
       </c>
       <c r="O2">
-        <v>29.45866666666666</v>
+        <v>29.29239901066666</v>
       </c>
       <c r="P2">
-        <v>93.28577777777775</v>
+        <v>92.75926353377776</v>
       </c>
       <c r="Q2">
-        <v>232.9857777777777</v>
+        <v>232.4592635337777</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08165397723801457</v>
+        <v>0.08192921989155891</v>
       </c>
       <c r="T2">
-        <v>0.4935434922969563</v>
+        <v>0.4973323110257006</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>177.1761710928712</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08149220769264331</v>
+        <v>0.0813304381472721</v>
       </c>
       <c r="C3">
-        <v>1379.492692510024</v>
+        <v>1367.530003206452</v>
       </c>
       <c r="D3">
-        <v>947.4656925100235</v>
+        <v>949.2760032064524</v>
       </c>
       <c r="E3">
-        <v>-1167.627</v>
+        <v>-1153.854</v>
       </c>
       <c r="F3">
-        <v>13.773</v>
+        <v>27.546</v>
       </c>
       <c r="G3">
         <v>445.8</v>
@@ -1533,28 +1533,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M3">
-        <v>0.6927819000000001</v>
+        <v>1.3855638</v>
       </c>
       <c r="N3">
-        <v>122.0516625444444</v>
+        <v>121.3588806444444</v>
       </c>
       <c r="O3">
-        <v>29.29239901066666</v>
+        <v>29.12613135466666</v>
       </c>
       <c r="P3">
-        <v>92.75926353377776</v>
+        <v>92.23274928977776</v>
       </c>
       <c r="Q3">
-        <v>232.4592635337777</v>
+        <v>231.9327492897777</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08192921989155891</v>
+        <v>0.08221007974211439</v>
       </c>
       <c r="T3">
-        <v>0.4973323110257006</v>
+        <v>0.5011984525856438</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>177.1761710928712</v>
+        <v>88.58808554643561</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0813304381472721</v>
+        <v>0.08116866860190085</v>
       </c>
       <c r="C4">
-        <v>1367.530003206452</v>
+        <v>1355.574245021513</v>
       </c>
       <c r="D4">
-        <v>949.2760032064524</v>
+        <v>951.093245021513</v>
       </c>
       <c r="E4">
-        <v>-1153.854</v>
+        <v>-1140.081</v>
       </c>
       <c r="F4">
-        <v>27.546</v>
+        <v>41.319</v>
       </c>
       <c r="G4">
         <v>445.8</v>
@@ -1615,28 +1615,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M4">
-        <v>1.3855638</v>
+        <v>2.0783457</v>
       </c>
       <c r="N4">
-        <v>121.3588806444444</v>
+        <v>120.6660987444444</v>
       </c>
       <c r="O4">
-        <v>29.12613135466666</v>
+        <v>28.95986369866666</v>
       </c>
       <c r="P4">
-        <v>92.23274928977776</v>
+        <v>91.70623504577776</v>
       </c>
       <c r="Q4">
-        <v>231.9327492897777</v>
+        <v>231.4062350457777</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08221007974211439</v>
+        <v>0.08249673051742357</v>
       </c>
       <c r="T4">
-        <v>0.5011984525856438</v>
+        <v>0.5051443084045548</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>88.58808554643561</v>
+        <v>59.05872369762375</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08116866860190085</v>
+        <v>0.08100689905652962</v>
       </c>
       <c r="C5">
-        <v>1355.574245021513</v>
+        <v>1343.62545783721</v>
       </c>
       <c r="D5">
-        <v>951.093245021513</v>
+        <v>952.9174578372097</v>
       </c>
       <c r="E5">
-        <v>-1140.081</v>
+        <v>-1126.308</v>
       </c>
       <c r="F5">
-        <v>41.319</v>
+        <v>55.09200000000001</v>
       </c>
       <c r="G5">
         <v>445.8</v>
@@ -1697,28 +1697,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M5">
-        <v>2.0783457</v>
+        <v>2.7711276</v>
       </c>
       <c r="N5">
-        <v>120.6660987444444</v>
+        <v>119.9733168444444</v>
       </c>
       <c r="O5">
-        <v>28.95986369866666</v>
+        <v>28.79359604266666</v>
       </c>
       <c r="P5">
-        <v>91.70623504577776</v>
+        <v>91.17972080177776</v>
       </c>
       <c r="Q5">
-        <v>231.4062350457777</v>
+        <v>230.8797208017778</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08249673051742357</v>
+        <v>0.08278935318388503</v>
       </c>
       <c r="T5">
-        <v>0.5051443084045548</v>
+        <v>0.5091723695530266</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.05872369762375</v>
+        <v>44.2940427732178</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08100689905652962</v>
+        <v>0.08084512951115838</v>
       </c>
       <c r="C6">
-        <v>1343.62545783721</v>
+        <v>1331.683681842114</v>
       </c>
       <c r="D6">
-        <v>952.9174578372097</v>
+        <v>954.7486818421143</v>
       </c>
       <c r="E6">
-        <v>-1126.308</v>
+        <v>-1112.535</v>
       </c>
       <c r="F6">
-        <v>55.09200000000001</v>
+        <v>68.86500000000001</v>
       </c>
       <c r="G6">
         <v>445.8</v>
@@ -1779,28 +1779,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M6">
-        <v>2.7711276</v>
+        <v>3.4639095</v>
       </c>
       <c r="N6">
-        <v>119.9733168444444</v>
+        <v>119.2805349444444</v>
       </c>
       <c r="O6">
-        <v>28.79359604266666</v>
+        <v>28.62732838666666</v>
       </c>
       <c r="P6">
-        <v>91.17972080177776</v>
+        <v>90.65320655777775</v>
       </c>
       <c r="Q6">
-        <v>230.8797208017778</v>
+        <v>230.3532065577778</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08278935318388503</v>
+        <v>0.08308813632753514</v>
       </c>
       <c r="T6">
-        <v>0.5091723695530266</v>
+        <v>0.5132852319888346</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.2940427732178</v>
+        <v>35.43523421857424</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08084512951115838</v>
+        <v>0.08068335996578715</v>
       </c>
       <c r="C7">
-        <v>1331.683681842114</v>
+        <v>1319.748957534315</v>
       </c>
       <c r="D7">
-        <v>954.7486818421143</v>
+        <v>956.5869575343145</v>
       </c>
       <c r="E7">
-        <v>-1112.535</v>
+        <v>-1098.762</v>
       </c>
       <c r="F7">
-        <v>68.86500000000001</v>
+        <v>82.63800000000002</v>
       </c>
       <c r="G7">
         <v>445.8</v>
@@ -1861,28 +1861,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M7">
-        <v>3.4639095</v>
+        <v>4.156691400000001</v>
       </c>
       <c r="N7">
-        <v>119.2805349444444</v>
+        <v>118.5877530444444</v>
       </c>
       <c r="O7">
-        <v>28.62732838666666</v>
+        <v>28.46106073066666</v>
       </c>
       <c r="P7">
-        <v>90.65320655777775</v>
+        <v>90.12669231377775</v>
       </c>
       <c r="Q7">
-        <v>230.3532065577778</v>
+        <v>229.8266923137778</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08308813632753514</v>
+        <v>0.08339327655934803</v>
       </c>
       <c r="T7">
-        <v>0.5132852319888346</v>
+        <v>0.5174856021360427</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.43523421857424</v>
+        <v>29.52936184881187</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08068335996578715</v>
+        <v>0.08052159042041591</v>
       </c>
       <c r="C8">
-        <v>1319.748957534315</v>
+        <v>1307.821325724401</v>
       </c>
       <c r="D8">
-        <v>956.5869575343145</v>
+        <v>958.4323257244008</v>
       </c>
       <c r="E8">
-        <v>-1098.762</v>
+        <v>-1084.989</v>
       </c>
       <c r="F8">
-        <v>82.63800000000001</v>
+        <v>96.411</v>
       </c>
       <c r="G8">
         <v>445.8</v>
@@ -1943,28 +1943,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M8">
-        <v>4.1566914</v>
+        <v>4.8494733</v>
       </c>
       <c r="N8">
-        <v>118.5877530444444</v>
+        <v>117.8949711444444</v>
       </c>
       <c r="O8">
-        <v>28.46106073066666</v>
+        <v>28.29479307466666</v>
       </c>
       <c r="P8">
-        <v>90.12669231377775</v>
+        <v>89.60017806977775</v>
       </c>
       <c r="Q8">
-        <v>229.8266923137778</v>
+        <v>229.3001780697778</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08339327655934803</v>
+        <v>0.08370497894668377</v>
       </c>
       <c r="T8">
-        <v>0.5174856021360427</v>
+        <v>0.521776302824051</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.52936184881187</v>
+        <v>25.31088158469589</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08052159042041591</v>
+        <v>0.08035982087504469</v>
       </c>
       <c r="C9">
-        <v>1307.821325724401</v>
+        <v>1295.900827538485</v>
       </c>
       <c r="D9">
-        <v>958.4323257244008</v>
+        <v>960.2848275384852</v>
       </c>
       <c r="E9">
-        <v>-1084.989</v>
+        <v>-1071.216</v>
       </c>
       <c r="F9">
-        <v>96.41100000000002</v>
+        <v>110.184</v>
       </c>
       <c r="G9">
         <v>445.8</v>
@@ -2025,28 +2025,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M9">
-        <v>4.849473300000001</v>
+        <v>5.5422552</v>
       </c>
       <c r="N9">
-        <v>117.8949711444444</v>
+        <v>117.2021892444444</v>
       </c>
       <c r="O9">
-        <v>28.29479307466666</v>
+        <v>28.12852541866666</v>
       </c>
       <c r="P9">
-        <v>89.60017806977775</v>
+        <v>89.07366382577776</v>
       </c>
       <c r="Q9">
-        <v>229.3001780697778</v>
+        <v>228.7736638257778</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08370497894668377</v>
+        <v>0.08402345747287465</v>
       </c>
       <c r="T9">
-        <v>0.521776302824051</v>
+        <v>0.5261602796139725</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.31088158469589</v>
+        <v>22.1470213866089</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08035982087504469</v>
+        <v>0.08019805132967345</v>
       </c>
       <c r="C10">
-        <v>1295.900827538485</v>
+        <v>1283.987504421258</v>
       </c>
       <c r="D10">
-        <v>960.2848275384852</v>
+        <v>962.144504421258</v>
       </c>
       <c r="E10">
-        <v>-1071.216</v>
+        <v>-1057.443</v>
       </c>
       <c r="F10">
-        <v>110.184</v>
+        <v>123.957</v>
       </c>
       <c r="G10">
         <v>445.8</v>
@@ -2107,28 +2107,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M10">
-        <v>5.5422552</v>
+        <v>6.2350371</v>
       </c>
       <c r="N10">
-        <v>117.2021892444444</v>
+        <v>116.5094073444444</v>
       </c>
       <c r="O10">
-        <v>28.12852541866666</v>
+        <v>27.96225776266666</v>
       </c>
       <c r="P10">
-        <v>89.07366382577776</v>
+        <v>88.54714958177776</v>
       </c>
       <c r="Q10">
-        <v>228.7736638257778</v>
+        <v>228.2471495817778</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08402345747287465</v>
+        <v>0.08434893552711367</v>
       </c>
       <c r="T10">
-        <v>0.5261602796139725</v>
+        <v>0.530640607542134</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.1470213866089</v>
+        <v>19.68624123254125</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08019805132967345</v>
+        <v>0.08003628178430222</v>
       </c>
       <c r="C11">
-        <v>1283.987504421258</v>
+        <v>1272.081398139077</v>
       </c>
       <c r="D11">
-        <v>962.144504421258</v>
+        <v>964.0113981390773</v>
       </c>
       <c r="E11">
-        <v>-1057.443</v>
+        <v>-1043.67</v>
       </c>
       <c r="F11">
-        <v>123.957</v>
+        <v>137.73</v>
       </c>
       <c r="G11">
         <v>445.8</v>
@@ -2189,28 +2189,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M11">
-        <v>6.2350371</v>
+        <v>6.927819</v>
       </c>
       <c r="N11">
-        <v>116.5094073444444</v>
+        <v>115.8166254444444</v>
       </c>
       <c r="O11">
-        <v>27.96225776266666</v>
+        <v>27.79599010666666</v>
       </c>
       <c r="P11">
-        <v>88.54714958177776</v>
+        <v>88.02063533777775</v>
       </c>
       <c r="Q11">
-        <v>228.2471495817778</v>
+        <v>227.7206353377777</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08434893552711367</v>
+        <v>0.08468164642700246</v>
       </c>
       <c r="T11">
-        <v>0.530640607542134</v>
+        <v>0.5352204983131438</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.68624123254125</v>
+        <v>17.71761710928712</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08003628178430222</v>
+        <v>0.07987451223893099</v>
       </c>
       <c r="C12">
-        <v>1272.081398139077</v>
+        <v>1260.182550783096</v>
       </c>
       <c r="D12">
-        <v>964.0113981390773</v>
+        <v>965.8855507830962</v>
       </c>
       <c r="E12">
-        <v>-1043.67</v>
+        <v>-1029.897</v>
       </c>
       <c r="F12">
-        <v>137.73</v>
+        <v>151.503</v>
       </c>
       <c r="G12">
         <v>445.8</v>
@@ -2271,28 +2271,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M12">
-        <v>6.927819</v>
+        <v>7.6206009</v>
       </c>
       <c r="N12">
-        <v>115.8166254444444</v>
+        <v>115.1238435444444</v>
       </c>
       <c r="O12">
-        <v>27.79599010666666</v>
+        <v>27.62972245066666</v>
       </c>
       <c r="P12">
-        <v>88.02063533777775</v>
+        <v>87.49412109377775</v>
       </c>
       <c r="Q12">
-        <v>227.7206353377777</v>
+        <v>227.1941210937777</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08468164642700246</v>
+        <v>0.08502183397632695</v>
       </c>
       <c r="T12">
-        <v>0.5352204983131438</v>
+        <v>0.5399033079778839</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.71761710928712</v>
+        <v>16.10692464480648</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07987451223893099</v>
+        <v>0.07971274269355974</v>
       </c>
       <c r="C13">
-        <v>1260.182550783096</v>
+        <v>1248.291004772427</v>
       </c>
       <c r="D13">
-        <v>965.8855507830962</v>
+        <v>967.7670047724265</v>
       </c>
       <c r="E13">
-        <v>-1029.897</v>
+        <v>-1016.124</v>
       </c>
       <c r="F13">
-        <v>151.503</v>
+        <v>165.276</v>
       </c>
       <c r="G13">
         <v>445.8</v>
@@ -2353,28 +2353,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M13">
-        <v>7.6206009</v>
+        <v>8.313382799999999</v>
       </c>
       <c r="N13">
-        <v>115.1238435444444</v>
+        <v>114.4310616444444</v>
       </c>
       <c r="O13">
-        <v>27.62972245066666</v>
+        <v>27.46345479466666</v>
       </c>
       <c r="P13">
-        <v>87.49412109377775</v>
+        <v>86.96760684977775</v>
       </c>
       <c r="Q13">
-        <v>227.1941210937777</v>
+        <v>226.6676068497777</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08502183397632695</v>
+        <v>0.08536975306086333</v>
       </c>
       <c r="T13">
-        <v>0.5399033079778839</v>
+        <v>0.5446925451350044</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.10692464480648</v>
+        <v>14.76468092440594</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07971274269355974</v>
+        <v>0.0795509731481885</v>
       </c>
       <c r="C14">
-        <v>1248.291004772427</v>
+        <v>1236.406802857339</v>
       </c>
       <c r="D14">
-        <v>967.7670047724265</v>
+        <v>969.6558028573385</v>
       </c>
       <c r="E14">
-        <v>-1016.124</v>
+        <v>-1002.351</v>
       </c>
       <c r="F14">
-        <v>165.276</v>
+        <v>179.049</v>
       </c>
       <c r="G14">
         <v>445.8</v>
@@ -2435,28 +2435,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M14">
-        <v>8.313382799999999</v>
+        <v>9.006164700000001</v>
       </c>
       <c r="N14">
-        <v>114.4310616444444</v>
+        <v>113.7382797444444</v>
       </c>
       <c r="O14">
-        <v>27.46345479466666</v>
+        <v>27.29718713866666</v>
       </c>
       <c r="P14">
-        <v>86.96760684977775</v>
+        <v>86.44109260577775</v>
       </c>
       <c r="Q14">
-        <v>226.6676068497777</v>
+        <v>226.1410926057777</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08536975306086333</v>
+        <v>0.08572567028527414</v>
       </c>
       <c r="T14">
-        <v>0.5446925451350044</v>
+        <v>0.5495918796980359</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.76468092440594</v>
+        <v>13.62893623791317</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0795509731481885</v>
+        <v>0.07954880360281727</v>
       </c>
       <c r="C15">
-        <v>1236.406802857339</v>
+        <v>1222.65918426258</v>
       </c>
       <c r="D15">
-        <v>969.6558028573385</v>
+        <v>969.6811842625797</v>
       </c>
       <c r="E15">
-        <v>-1002.351</v>
+        <v>-988.5780000000001</v>
       </c>
       <c r="F15">
-        <v>179.049</v>
+        <v>192.822</v>
       </c>
       <c r="G15">
         <v>445.8</v>
@@ -2517,45 +2517,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M15">
-        <v>9.006164700000001</v>
+        <v>9.988179600000002</v>
       </c>
       <c r="N15">
-        <v>113.7382797444444</v>
+        <v>112.7562648444444</v>
       </c>
       <c r="O15">
-        <v>27.29718713866666</v>
+        <v>27.06150356266666</v>
       </c>
       <c r="P15">
-        <v>86.44109260577775</v>
+        <v>85.69476128177776</v>
       </c>
       <c r="Q15">
-        <v>226.1410926057777</v>
+        <v>225.3947612817777</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08572567028527414</v>
+        <v>0.08608986465443869</v>
       </c>
       <c r="T15">
-        <v>0.5495918796980359</v>
+        <v>0.5546051522741611</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.62893623791317</v>
+        <v>12.28897049913324</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07954880360281727</v>
+        <v>0.07939843405744604</v>
       </c>
       <c r="C16">
-        <v>1222.65918426258</v>
+        <v>1210.648593663491</v>
       </c>
       <c r="D16">
-        <v>969.6811842625797</v>
+        <v>971.4435936634909</v>
       </c>
       <c r="E16">
-        <v>-988.5780000000001</v>
+        <v>-974.8050000000001</v>
       </c>
       <c r="F16">
-        <v>192.822</v>
+        <v>206.5950000000001</v>
       </c>
       <c r="G16">
         <v>445.8</v>
@@ -2599,28 +2599,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M16">
-        <v>9.988179600000002</v>
+        <v>10.701621</v>
       </c>
       <c r="N16">
-        <v>112.7562648444444</v>
+        <v>112.0428234444444</v>
       </c>
       <c r="O16">
-        <v>27.06150356266666</v>
+        <v>26.89027762666666</v>
       </c>
       <c r="P16">
-        <v>85.69476128177776</v>
+        <v>85.15254581777775</v>
       </c>
       <c r="Q16">
-        <v>225.3947612817777</v>
+        <v>224.8525458177778</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08608986465443869</v>
+        <v>0.08646262830287769</v>
       </c>
       <c r="T16">
-        <v>0.5546051522741611</v>
+        <v>0.5597363842050187</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.28897049913324</v>
+        <v>11.46970579919102</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07939843405744602</v>
+        <v>0.07924806451207481</v>
       </c>
       <c r="C17">
-        <v>1210.648593663491</v>
+        <v>1198.644421137854</v>
       </c>
       <c r="D17">
-        <v>971.4435936634911</v>
+        <v>973.2124211378543</v>
       </c>
       <c r="E17">
-        <v>-974.8050000000001</v>
+        <v>-961.032</v>
       </c>
       <c r="F17">
-        <v>206.595</v>
+        <v>220.368</v>
       </c>
       <c r="G17">
         <v>445.8</v>
@@ -2681,28 +2681,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M17">
-        <v>10.701621</v>
+        <v>11.4150624</v>
       </c>
       <c r="N17">
-        <v>112.0428234444444</v>
+        <v>111.3293820444444</v>
       </c>
       <c r="O17">
-        <v>26.89027762666666</v>
+        <v>26.71905169066666</v>
       </c>
       <c r="P17">
-        <v>85.15254581777775</v>
+        <v>84.61033035377775</v>
       </c>
       <c r="Q17">
-        <v>224.8525458177778</v>
+        <v>224.3103303537777</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08646262830287768</v>
+        <v>0.08684426727627953</v>
       </c>
       <c r="T17">
-        <v>0.5597363842050186</v>
+        <v>0.5649897883247061</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.46970579919102</v>
+        <v>10.75284918674158</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07924806451207481</v>
+        <v>0.07909769496670357</v>
       </c>
       <c r="C18">
-        <v>1198.644421137854</v>
+        <v>1186.646701808162</v>
       </c>
       <c r="D18">
-        <v>973.2124211378543</v>
+        <v>974.9877018081619</v>
       </c>
       <c r="E18">
-        <v>-961.032</v>
+        <v>-947.259</v>
       </c>
       <c r="F18">
-        <v>220.368</v>
+        <v>234.141</v>
       </c>
       <c r="G18">
         <v>445.8</v>
@@ -2763,28 +2763,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M18">
-        <v>11.4150624</v>
+        <v>12.1285038</v>
       </c>
       <c r="N18">
-        <v>111.3293820444444</v>
+        <v>110.6159406444444</v>
       </c>
       <c r="O18">
-        <v>26.71905169066666</v>
+        <v>26.54782575466666</v>
       </c>
       <c r="P18">
-        <v>84.61033035377775</v>
+        <v>84.06811488977775</v>
       </c>
       <c r="Q18">
-        <v>224.3103303537777</v>
+        <v>223.7681148897777</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08684426727627953</v>
+        <v>0.08723510236952238</v>
       </c>
       <c r="T18">
-        <v>0.5649897883247061</v>
+        <v>0.5703697804954705</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.75284918674158</v>
+        <v>10.12032864634502</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07909769496670357</v>
+        <v>0.07917988542133234</v>
       </c>
       <c r="C19">
-        <v>1186.646701808162</v>
+        <v>1171.902549798114</v>
       </c>
       <c r="D19">
-        <v>974.9877018081619</v>
+        <v>974.0165497981137</v>
       </c>
       <c r="E19">
-        <v>-947.259</v>
+        <v>-933.486</v>
       </c>
       <c r="F19">
-        <v>234.141</v>
+        <v>247.9140000000001</v>
       </c>
       <c r="G19">
         <v>445.8</v>
@@ -2845,45 +2845,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M19">
-        <v>12.1285038</v>
+        <v>13.263399</v>
       </c>
       <c r="N19">
-        <v>110.6159406444444</v>
+        <v>109.4810454444444</v>
       </c>
       <c r="O19">
-        <v>26.54782575466666</v>
+        <v>26.27545090666666</v>
       </c>
       <c r="P19">
-        <v>84.06811488977775</v>
+        <v>83.20559453777776</v>
       </c>
       <c r="Q19">
-        <v>223.7681148897777</v>
+        <v>222.9055945377777</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08723510236952238</v>
+        <v>0.08763547002601504</v>
       </c>
       <c r="T19">
-        <v>0.5703697804954705</v>
+        <v>0.5758809919874729</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.12032864634502</v>
+        <v>9.254373214923593</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07917988542133234</v>
+        <v>0.0790424358759611</v>
       </c>
       <c r="C20">
-        <v>1171.902549798114</v>
+        <v>1159.754725671603</v>
       </c>
       <c r="D20">
-        <v>974.0165497981137</v>
+        <v>975.6417256716032</v>
       </c>
       <c r="E20">
-        <v>-933.4860000000001</v>
+        <v>-919.7130000000001</v>
       </c>
       <c r="F20">
-        <v>247.914</v>
+        <v>261.687</v>
       </c>
       <c r="G20">
         <v>445.8</v>
@@ -2927,28 +2927,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M20">
-        <v>13.263399</v>
+        <v>14.0002545</v>
       </c>
       <c r="N20">
-        <v>109.4810454444444</v>
+        <v>108.7441899444444</v>
       </c>
       <c r="O20">
-        <v>26.27545090666666</v>
+        <v>26.09860558666666</v>
       </c>
       <c r="P20">
-        <v>83.20559453777776</v>
+        <v>82.64558435777775</v>
       </c>
       <c r="Q20">
-        <v>222.9055945377777</v>
+        <v>222.3455843577777</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08763547002601504</v>
+        <v>0.08804572330365568</v>
       </c>
       <c r="T20">
-        <v>0.5758809919874729</v>
+        <v>0.5815282827755741</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.254373214923596</v>
+        <v>8.767300940453932</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0790424358759611</v>
+        <v>0.07890498633058986</v>
       </c>
       <c r="C21">
-        <v>1159.754725671603</v>
+        <v>1147.612333918705</v>
       </c>
       <c r="D21">
-        <v>975.6417256716032</v>
+        <v>977.2723339187045</v>
       </c>
       <c r="E21">
-        <v>-919.7130000000001</v>
+        <v>-905.9400000000001</v>
       </c>
       <c r="F21">
-        <v>261.687</v>
+        <v>275.46</v>
       </c>
       <c r="G21">
         <v>445.8</v>
@@ -3009,28 +3009,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M21">
-        <v>14.0002545</v>
+        <v>14.73711</v>
       </c>
       <c r="N21">
-        <v>108.7441899444444</v>
+        <v>108.0073344444444</v>
       </c>
       <c r="O21">
-        <v>26.09860558666666</v>
+        <v>25.92176026666666</v>
       </c>
       <c r="P21">
-        <v>82.64558435777775</v>
+        <v>82.08557417777776</v>
       </c>
       <c r="Q21">
-        <v>222.3455843577777</v>
+        <v>221.7855741777777</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08804572330365568</v>
+        <v>0.08846623291323732</v>
       </c>
       <c r="T21">
-        <v>0.5815282827755741</v>
+        <v>0.5873167558333779</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.767300940453932</v>
+        <v>8.328935893431236</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07890498633058986</v>
+        <v>0.07876753678521864</v>
       </c>
       <c r="C22">
-        <v>1147.612333918705</v>
+        <v>1135.475401822698</v>
       </c>
       <c r="D22">
-        <v>977.2723339187045</v>
+        <v>978.9084018226982</v>
       </c>
       <c r="E22">
-        <v>-905.9400000000001</v>
+        <v>-892.167</v>
       </c>
       <c r="F22">
-        <v>275.46</v>
+        <v>289.2330000000001</v>
       </c>
       <c r="G22">
         <v>445.8</v>
@@ -3091,28 +3091,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M22">
-        <v>14.73711</v>
+        <v>15.4739655</v>
       </c>
       <c r="N22">
-        <v>108.0073344444444</v>
+        <v>107.2704789444444</v>
       </c>
       <c r="O22">
-        <v>25.92176026666666</v>
+        <v>25.74491494666666</v>
       </c>
       <c r="P22">
-        <v>82.08557417777776</v>
+        <v>81.52556399777775</v>
       </c>
       <c r="Q22">
-        <v>221.7855741777777</v>
+        <v>221.2255639977777</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08846623291323732</v>
+        <v>0.08889738833571978</v>
       </c>
       <c r="T22">
-        <v>0.5873167558333779</v>
+        <v>0.5932517725128983</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.328935893431236</v>
+        <v>7.932319898505938</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07876753678521864</v>
+        <v>0.0787638472398474</v>
       </c>
       <c r="C23">
-        <v>1135.475401822698</v>
+        <v>1121.746394140194</v>
       </c>
       <c r="D23">
-        <v>978.9084018226982</v>
+        <v>978.9523941401936</v>
       </c>
       <c r="E23">
-        <v>-892.1670000000001</v>
+        <v>-878.394</v>
       </c>
       <c r="F23">
-        <v>289.233</v>
+        <v>303.006</v>
       </c>
       <c r="G23">
         <v>445.8</v>
@@ -3173,45 +3173,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M23">
-        <v>15.4739655</v>
+        <v>16.4532258</v>
       </c>
       <c r="N23">
-        <v>107.2704789444444</v>
+        <v>106.2912186444444</v>
       </c>
       <c r="O23">
-        <v>25.74491494666666</v>
+        <v>25.50989247466666</v>
       </c>
       <c r="P23">
-        <v>81.52556399777775</v>
+        <v>80.78132616977776</v>
       </c>
       <c r="Q23">
-        <v>221.2255639977777</v>
+        <v>220.4813261697777</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08889738833571978</v>
+        <v>0.08933959902544539</v>
       </c>
       <c r="T23">
-        <v>0.5932517725128983</v>
+        <v>0.5993389691072782</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.93231989850594</v>
+        <v>7.460205429408524</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0787638472398474</v>
+        <v>0.07863247769447615</v>
       </c>
       <c r="C24">
-        <v>1121.746394140194</v>
+        <v>1109.542360694632</v>
       </c>
       <c r="D24">
-        <v>978.9523941401936</v>
+        <v>980.5213606946321</v>
       </c>
       <c r="E24">
-        <v>-878.394</v>
+        <v>-864.6210000000001</v>
       </c>
       <c r="F24">
-        <v>303.006</v>
+        <v>316.7790000000001</v>
       </c>
       <c r="G24">
         <v>445.8</v>
@@ -3255,28 +3255,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M24">
-        <v>16.4532258</v>
+        <v>17.2010997</v>
       </c>
       <c r="N24">
-        <v>106.2912186444444</v>
+        <v>105.5433447444444</v>
       </c>
       <c r="O24">
-        <v>25.50989247466666</v>
+        <v>25.33040273866666</v>
       </c>
       <c r="P24">
-        <v>80.78132616977776</v>
+        <v>80.21294200577776</v>
       </c>
       <c r="Q24">
-        <v>220.4813261697777</v>
+        <v>219.9129420057778</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08933959902544539</v>
+        <v>0.08979329570711189</v>
       </c>
       <c r="T24">
-        <v>0.5993389691072782</v>
+        <v>0.6055842747041095</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.460205429408524</v>
+        <v>7.135848671608152</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07863247769447615</v>
+        <v>0.07850110814910491</v>
       </c>
       <c r="C25">
-        <v>1109.542360694632</v>
+        <v>1097.343364486207</v>
       </c>
       <c r="D25">
-        <v>980.5213606946321</v>
+        <v>982.0953644862068</v>
       </c>
       <c r="E25">
-        <v>-864.6210000000001</v>
+        <v>-850.848</v>
       </c>
       <c r="F25">
-        <v>316.7790000000001</v>
+        <v>330.5520000000001</v>
       </c>
       <c r="G25">
         <v>445.8</v>
@@ -3337,28 +3337,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M25">
-        <v>17.2010997</v>
+        <v>17.94897360000001</v>
       </c>
       <c r="N25">
-        <v>105.5433447444444</v>
+        <v>104.7954708444444</v>
       </c>
       <c r="O25">
-        <v>25.33040273866666</v>
+        <v>25.15091300266666</v>
       </c>
       <c r="P25">
-        <v>80.21294200577776</v>
+        <v>79.64455784177775</v>
       </c>
       <c r="Q25">
-        <v>219.9129420057778</v>
+        <v>219.3445578417777</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08979329570711189</v>
+        <v>0.09025893177513805</v>
       </c>
       <c r="T25">
-        <v>0.6055842747041095</v>
+        <v>0.6119939304482258</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.135848671608152</v>
+        <v>6.838521643624478</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07850110814910491</v>
+        <v>0.0783697386037337</v>
       </c>
       <c r="C26">
-        <v>1097.343364486207</v>
+        <v>1085.149429812333</v>
       </c>
       <c r="D26">
-        <v>982.0953644862068</v>
+        <v>983.6744298123334</v>
       </c>
       <c r="E26">
-        <v>-850.8480000000001</v>
+        <v>-837.075</v>
       </c>
       <c r="F26">
-        <v>330.552</v>
+        <v>344.325</v>
       </c>
       <c r="G26">
         <v>445.8</v>
@@ -3419,28 +3419,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M26">
-        <v>17.9489736</v>
+        <v>18.6968475</v>
       </c>
       <c r="N26">
-        <v>104.7954708444444</v>
+        <v>104.0475969444444</v>
       </c>
       <c r="O26">
-        <v>25.15091300266666</v>
+        <v>24.97142326666666</v>
       </c>
       <c r="P26">
-        <v>79.64455784177775</v>
+        <v>79.07617367777775</v>
       </c>
       <c r="Q26">
-        <v>219.3445578417777</v>
+        <v>218.7761736777777</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09025893177513805</v>
+        <v>0.09073698480497826</v>
       </c>
       <c r="T26">
-        <v>0.6119939304482258</v>
+        <v>0.6185745103455186</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.83852164362448</v>
+        <v>6.5649807778795</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0783697386037337</v>
+        <v>0.07823836905836246</v>
       </c>
       <c r="C27">
-        <v>1085.149429812333</v>
+        <v>1072.960581126947</v>
       </c>
       <c r="D27">
-        <v>983.6744298123334</v>
+        <v>985.258581126947</v>
       </c>
       <c r="E27">
-        <v>-837.075</v>
+        <v>-823.302</v>
       </c>
       <c r="F27">
-        <v>344.325</v>
+        <v>358.0980000000001</v>
       </c>
       <c r="G27">
         <v>445.8</v>
@@ -3501,28 +3501,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M27">
-        <v>18.6968475</v>
+        <v>19.44472140000001</v>
       </c>
       <c r="N27">
-        <v>104.0475969444444</v>
+        <v>103.2997230444444</v>
       </c>
       <c r="O27">
-        <v>24.97142326666666</v>
+        <v>24.79193353066666</v>
       </c>
       <c r="P27">
-        <v>79.07617367777775</v>
+        <v>78.50778951377775</v>
       </c>
       <c r="Q27">
-        <v>218.7761736777777</v>
+        <v>218.2077895137778</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09073698480497826</v>
+        <v>0.09122795818697629</v>
       </c>
       <c r="T27">
-        <v>0.6185745103455186</v>
+        <v>0.6253329437535489</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.5649807778795</v>
+        <v>6.312481517191826</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07823836905836246</v>
+        <v>0.07831219951299123</v>
       </c>
       <c r="C28">
-        <v>1072.960581126947</v>
+        <v>1058.296651381574</v>
       </c>
       <c r="D28">
-        <v>985.258581126947</v>
+        <v>984.3676513815738</v>
       </c>
       <c r="E28">
-        <v>-823.302</v>
+        <v>-809.529</v>
       </c>
       <c r="F28">
-        <v>358.0980000000001</v>
+        <v>371.8710000000001</v>
       </c>
       <c r="G28">
         <v>445.8</v>
@@ -3583,45 +3583,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M28">
-        <v>19.44472140000001</v>
+        <v>20.56446630000001</v>
       </c>
       <c r="N28">
-        <v>103.2997230444444</v>
+        <v>102.1799781444444</v>
       </c>
       <c r="O28">
-        <v>24.79193353066666</v>
+        <v>24.52319475466665</v>
       </c>
       <c r="P28">
-        <v>78.50778951377775</v>
+        <v>77.65678338977776</v>
       </c>
       <c r="Q28">
-        <v>218.2077895137778</v>
+        <v>217.3567833897777</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09122795818697629</v>
+        <v>0.09173238289450852</v>
       </c>
       <c r="T28">
-        <v>0.6253329437535489</v>
+        <v>0.6322765397207034</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.312481517191826</v>
+        <v>5.968763918003765</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07831219951299123</v>
+        <v>0.07818842996761999</v>
       </c>
       <c r="C29">
-        <v>1058.296651381574</v>
+        <v>1046.018122984076</v>
       </c>
       <c r="D29">
-        <v>984.3676513815738</v>
+        <v>985.8621229840761</v>
       </c>
       <c r="E29">
-        <v>-809.529</v>
+        <v>-795.7560000000001</v>
       </c>
       <c r="F29">
-        <v>371.8710000000001</v>
+        <v>385.6440000000001</v>
       </c>
       <c r="G29">
         <v>445.8</v>
@@ -3665,28 +3665,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M29">
-        <v>20.56446630000001</v>
+        <v>21.32611320000001</v>
       </c>
       <c r="N29">
-        <v>102.1799781444444</v>
+        <v>101.4183312444444</v>
       </c>
       <c r="O29">
-        <v>24.52319475466665</v>
+        <v>24.34039949866666</v>
       </c>
       <c r="P29">
-        <v>77.65678338977776</v>
+        <v>77.07793174577775</v>
       </c>
       <c r="Q29">
-        <v>217.3567833897777</v>
+        <v>216.7779317457777</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09173238289450852</v>
+        <v>0.0922508193994722</v>
       </c>
       <c r="T29">
-        <v>0.6322765397207034</v>
+        <v>0.6394130133536122</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.968763918003765</v>
+        <v>5.755593778075059</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07818842996761999</v>
+        <v>0.07806466042224874</v>
       </c>
       <c r="C30">
-        <v>1046.018122984076</v>
+        <v>1033.74413931405</v>
       </c>
       <c r="D30">
-        <v>985.8621229840761</v>
+        <v>987.3611393140501</v>
       </c>
       <c r="E30">
-        <v>-795.7560000000001</v>
+        <v>-781.9829999999999</v>
       </c>
       <c r="F30">
-        <v>385.6440000000001</v>
+        <v>399.4170000000001</v>
       </c>
       <c r="G30">
         <v>445.8</v>
@@ -3747,28 +3747,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M30">
-        <v>21.32611320000001</v>
+        <v>22.0877601</v>
       </c>
       <c r="N30">
-        <v>101.4183312444444</v>
+        <v>100.6566843444444</v>
       </c>
       <c r="O30">
-        <v>24.34039949866666</v>
+        <v>24.15760424266666</v>
       </c>
       <c r="P30">
-        <v>77.07793174577775</v>
+        <v>76.49908010177776</v>
       </c>
       <c r="Q30">
-        <v>216.7779317457777</v>
+        <v>216.1990801017778</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0922508193994722</v>
+        <v>0.09278385974964612</v>
       </c>
       <c r="T30">
-        <v>0.6394130133536122</v>
+        <v>0.6467505144128002</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.755593778075059</v>
+        <v>5.557125027106954</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07806466042224874</v>
+        <v>0.07794089087687751</v>
       </c>
       <c r="C31">
-        <v>1033.74413931405</v>
+        <v>1021.474721134019</v>
       </c>
       <c r="D31">
-        <v>987.3611393140501</v>
+        <v>988.8647211340191</v>
       </c>
       <c r="E31">
-        <v>-781.9830000000001</v>
+        <v>-768.21</v>
       </c>
       <c r="F31">
-        <v>399.417</v>
+        <v>413.1900000000001</v>
       </c>
       <c r="G31">
         <v>445.8</v>
@@ -3829,28 +3829,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M31">
-        <v>22.0877601</v>
+        <v>22.849407</v>
       </c>
       <c r="N31">
-        <v>100.6566843444444</v>
+        <v>99.89503744444441</v>
       </c>
       <c r="O31">
-        <v>24.15760424266666</v>
+        <v>23.97480898666666</v>
       </c>
       <c r="P31">
-        <v>76.49908010177776</v>
+        <v>75.92022845777775</v>
       </c>
       <c r="Q31">
-        <v>216.1990801017778</v>
+        <v>215.6202284577777</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09278385974964612</v>
+        <v>0.09333212982411074</v>
       </c>
       <c r="T31">
-        <v>0.6467505144128002</v>
+        <v>0.6542976583593934</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.557125027106954</v>
+        <v>5.371887526203389</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07794089087687751</v>
+        <v>0.07781712133150627</v>
       </c>
       <c r="C32">
-        <v>1021.474721134019</v>
+        <v>1009.209889333171</v>
       </c>
       <c r="D32">
-        <v>988.8647211340191</v>
+        <v>990.372889333171</v>
       </c>
       <c r="E32">
-        <v>-768.21</v>
+        <v>-754.437</v>
       </c>
       <c r="F32">
-        <v>413.1900000000001</v>
+        <v>426.9630000000001</v>
       </c>
       <c r="G32">
         <v>445.8</v>
@@ -3911,28 +3911,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M32">
-        <v>22.849407</v>
+        <v>23.61105390000001</v>
       </c>
       <c r="N32">
-        <v>99.89503744444441</v>
+        <v>99.13339054444441</v>
       </c>
       <c r="O32">
-        <v>23.97480898666666</v>
+        <v>23.79201373066666</v>
       </c>
       <c r="P32">
-        <v>75.92022845777775</v>
+        <v>75.34137681377776</v>
       </c>
       <c r="Q32">
-        <v>215.6202284577777</v>
+        <v>215.0413768137777</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09333212982411074</v>
+        <v>0.09389629178479171</v>
       </c>
       <c r="T32">
-        <v>0.6542976583593934</v>
+        <v>0.6620635601015402</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.371887526203389</v>
+        <v>5.198600831809731</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07781712133150627</v>
+        <v>0.07769335178613504</v>
       </c>
       <c r="C33">
-        <v>1009.209889333171</v>
+        <v>996.949664928324</v>
       </c>
       <c r="D33">
-        <v>990.372889333171</v>
+        <v>991.885664928324</v>
       </c>
       <c r="E33">
-        <v>-754.437</v>
+        <v>-740.664</v>
       </c>
       <c r="F33">
-        <v>426.9630000000001</v>
+        <v>440.736</v>
       </c>
       <c r="G33">
         <v>445.8</v>
@@ -3993,28 +3993,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M33">
-        <v>23.61105390000001</v>
+        <v>24.3727008</v>
       </c>
       <c r="N33">
-        <v>99.13339054444441</v>
+        <v>98.37174364444441</v>
       </c>
       <c r="O33">
-        <v>23.79201373066666</v>
+        <v>23.60921847466666</v>
       </c>
       <c r="P33">
-        <v>75.34137681377776</v>
+        <v>74.76252516977775</v>
       </c>
       <c r="Q33">
-        <v>215.0413768137777</v>
+        <v>214.4625251697777</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09389629178479171</v>
+        <v>0.09447704674431624</v>
       </c>
       <c r="T33">
-        <v>0.6620635601015402</v>
+        <v>0.6700578707184559</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.198600831809731</v>
+        <v>5.036144555815677</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07769335178613504</v>
+        <v>0.07756958224076381</v>
       </c>
       <c r="C34">
-        <v>996.949664928324</v>
+        <v>984.6940690649046</v>
       </c>
       <c r="D34">
-        <v>991.885664928324</v>
+        <v>993.4030690649046</v>
       </c>
       <c r="E34">
-        <v>-740.664</v>
+        <v>-726.8910000000001</v>
       </c>
       <c r="F34">
-        <v>440.736</v>
+        <v>454.5090000000001</v>
       </c>
       <c r="G34">
         <v>445.8</v>
@@ -4075,28 +4075,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M34">
-        <v>24.3727008</v>
+        <v>25.13434770000001</v>
       </c>
       <c r="N34">
-        <v>98.37174364444441</v>
+        <v>97.61009674444441</v>
       </c>
       <c r="O34">
-        <v>23.60921847466666</v>
+        <v>23.42642321866666</v>
       </c>
       <c r="P34">
-        <v>74.76252516977775</v>
+        <v>74.18367352577775</v>
       </c>
       <c r="Q34">
-        <v>214.4625251697777</v>
+        <v>213.8836735257777</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09447704674431624</v>
+        <v>0.09507513767278181</v>
       </c>
       <c r="T34">
-        <v>0.6700578707184559</v>
+        <v>0.67829081747319</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.036144555815677</v>
+        <v>4.883534114730352</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07756958224076381</v>
+        <v>0.07744581269539257</v>
       </c>
       <c r="C35">
-        <v>984.6940690649046</v>
+        <v>972.4431230179321</v>
       </c>
       <c r="D35">
-        <v>993.4030690649046</v>
+        <v>994.9251230179323</v>
       </c>
       <c r="E35">
-        <v>-726.8910000000001</v>
+        <v>-713.1179999999999</v>
       </c>
       <c r="F35">
-        <v>454.5090000000001</v>
+        <v>468.2820000000001</v>
       </c>
       <c r="G35">
         <v>445.8</v>
@@ -4157,28 +4157,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M35">
-        <v>25.13434770000001</v>
+        <v>25.89599460000001</v>
       </c>
       <c r="N35">
-        <v>97.61009674444441</v>
+        <v>96.8484498444444</v>
       </c>
       <c r="O35">
-        <v>23.42642321866666</v>
+        <v>23.24362796266666</v>
       </c>
       <c r="P35">
-        <v>74.18367352577775</v>
+        <v>73.60482188177775</v>
       </c>
       <c r="Q35">
-        <v>213.8836735257777</v>
+        <v>213.3048218817777</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09507513767278181</v>
+        <v>0.09569135256877663</v>
       </c>
       <c r="T35">
-        <v>0.67829081747319</v>
+        <v>0.6867732474629161</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.883534114730352</v>
+        <v>4.739900758414755</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07744581269539257</v>
+        <v>0.07732204315002134</v>
       </c>
       <c r="C36">
-        <v>972.4431230179321</v>
+        <v>960.1968481930128</v>
       </c>
       <c r="D36">
-        <v>994.9251230179323</v>
+        <v>996.4518481930129</v>
       </c>
       <c r="E36">
-        <v>-713.1179999999999</v>
+        <v>-699.345</v>
       </c>
       <c r="F36">
-        <v>468.2820000000001</v>
+        <v>482.0550000000001</v>
       </c>
       <c r="G36">
         <v>445.8</v>
@@ -4239,28 +4239,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M36">
-        <v>25.89599460000001</v>
+        <v>26.65764150000001</v>
       </c>
       <c r="N36">
-        <v>96.8484498444444</v>
+        <v>96.0868029444444</v>
       </c>
       <c r="O36">
-        <v>23.24362796266666</v>
+        <v>23.06083270666666</v>
       </c>
       <c r="P36">
-        <v>73.60482188177775</v>
+        <v>73.02597023777774</v>
       </c>
       <c r="Q36">
-        <v>213.3048218817777</v>
+        <v>212.7259702377777</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09569135256877663</v>
+        <v>0.09632652792310975</v>
       </c>
       <c r="T36">
-        <v>0.6867732474629161</v>
+        <v>0.6955166752984799</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.739900758414755</v>
+        <v>4.604475022460047</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07732204315002134</v>
+        <v>0.07788227360465011</v>
       </c>
       <c r="C37">
-        <v>960.1968481930128</v>
+        <v>939.550416799498</v>
       </c>
       <c r="D37">
-        <v>996.4518481930129</v>
+        <v>989.5784167994982</v>
       </c>
       <c r="E37">
-        <v>-699.345</v>
+        <v>-685.5719999999999</v>
       </c>
       <c r="F37">
-        <v>482.0550000000001</v>
+        <v>495.8280000000001</v>
       </c>
       <c r="G37">
         <v>445.8</v>
@@ -4321,45 +4321,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M37">
-        <v>26.65764150000001</v>
+        <v>28.65885840000001</v>
       </c>
       <c r="N37">
-        <v>96.0868029444444</v>
+        <v>94.0855860444444</v>
       </c>
       <c r="O37">
-        <v>23.06083270666666</v>
+        <v>22.58054065066666</v>
       </c>
       <c r="P37">
-        <v>73.02597023777774</v>
+        <v>71.50504539377775</v>
       </c>
       <c r="Q37">
-        <v>212.7259702377777</v>
+        <v>211.2050453937777</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09632652792310975</v>
+        <v>0.0969815525072658</v>
       </c>
       <c r="T37">
-        <v>0.6955166752984799</v>
+        <v>0.7045333352539052</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.24</v>
       </c>
       <c r="W37">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.604475022460047</v>
+        <v>4.282949541508756</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07788227360465011</v>
+        <v>0.07777750405927887</v>
       </c>
       <c r="C38">
-        <v>939.5504167994982</v>
+        <v>927.0556098193827</v>
       </c>
       <c r="D38">
-        <v>989.5784167994982</v>
+        <v>990.8566098193827</v>
       </c>
       <c r="E38">
-        <v>-685.5720000000001</v>
+        <v>-671.799</v>
       </c>
       <c r="F38">
-        <v>495.828</v>
+        <v>509.6010000000001</v>
       </c>
       <c r="G38">
         <v>445.8</v>
@@ -4403,28 +4403,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M38">
-        <v>28.6588584</v>
+        <v>29.45493780000001</v>
       </c>
       <c r="N38">
-        <v>94.08558604444441</v>
+        <v>93.2895066444444</v>
       </c>
       <c r="O38">
-        <v>22.58054065066666</v>
+        <v>22.38948159466666</v>
       </c>
       <c r="P38">
-        <v>71.50504539377775</v>
+        <v>70.90002504977775</v>
       </c>
       <c r="Q38">
-        <v>211.2050453937777</v>
+        <v>210.6000250497777</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09698155250726578</v>
+        <v>0.09765737152266488</v>
       </c>
       <c r="T38">
-        <v>0.704533335253905</v>
+        <v>0.7138362383825183</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.282949541508757</v>
+        <v>4.167194148495007</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07777750405927887</v>
+        <v>0.07767273451390763</v>
       </c>
       <c r="C39">
-        <v>927.0556098193827</v>
+        <v>914.5641090762927</v>
       </c>
       <c r="D39">
-        <v>990.8566098193827</v>
+        <v>992.1381090762926</v>
       </c>
       <c r="E39">
-        <v>-671.799</v>
+        <v>-658.0260000000001</v>
       </c>
       <c r="F39">
-        <v>509.6010000000001</v>
+        <v>523.374</v>
       </c>
       <c r="G39">
         <v>445.8</v>
@@ -4485,28 +4485,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M39">
-        <v>29.45493780000001</v>
+        <v>30.2510172</v>
       </c>
       <c r="N39">
-        <v>93.2895066444444</v>
+        <v>92.4934272444444</v>
       </c>
       <c r="O39">
-        <v>22.38948159466666</v>
+        <v>22.19842253866666</v>
       </c>
       <c r="P39">
-        <v>70.90002504977775</v>
+        <v>70.29500470577776</v>
       </c>
       <c r="Q39">
-        <v>210.6000250497777</v>
+        <v>209.9950047057777</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09765737152266488</v>
+        <v>0.09835499115146393</v>
       </c>
       <c r="T39">
-        <v>0.7138362383825183</v>
+        <v>0.7234392351604417</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.167194148495007</v>
+        <v>4.057531144587244</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07767273451390763</v>
+        <v>0.0786053649685364</v>
       </c>
       <c r="C40">
-        <v>914.5641090762927</v>
+        <v>889.4987984113221</v>
       </c>
       <c r="D40">
-        <v>992.1381090762926</v>
+        <v>980.8457984113221</v>
       </c>
       <c r="E40">
-        <v>-658.0260000000001</v>
+        <v>-644.253</v>
       </c>
       <c r="F40">
-        <v>523.374</v>
+        <v>537.147</v>
       </c>
       <c r="G40">
         <v>445.8</v>
@@ -4567,45 +4567,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M40">
-        <v>30.2510172</v>
+        <v>32.9271111</v>
       </c>
       <c r="N40">
-        <v>92.4934272444444</v>
+        <v>89.81733334444441</v>
       </c>
       <c r="O40">
-        <v>22.19842253866666</v>
+        <v>21.55616000266666</v>
       </c>
       <c r="P40">
-        <v>70.29500470577776</v>
+        <v>68.26117334177775</v>
       </c>
       <c r="Q40">
-        <v>209.9950047057777</v>
+        <v>207.9611733417777</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09835499115146393</v>
+        <v>0.09907548355497771</v>
       </c>
       <c r="T40">
-        <v>0.7234392351604417</v>
+        <v>0.7333570842917396</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.057531144587244</v>
+        <v>3.727762331522743</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0786053649685364</v>
+        <v>0.07852719542316516</v>
       </c>
       <c r="C41">
-        <v>889.4987984113221</v>
+        <v>876.6623979090041</v>
       </c>
       <c r="D41">
-        <v>980.8457984113221</v>
+        <v>981.7823979090042</v>
       </c>
       <c r="E41">
-        <v>-644.253</v>
+        <v>-630.48</v>
       </c>
       <c r="F41">
-        <v>537.147</v>
+        <v>550.9200000000001</v>
       </c>
       <c r="G41">
         <v>445.8</v>
@@ -4649,28 +4649,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M41">
-        <v>32.9271111</v>
+        <v>33.771396</v>
       </c>
       <c r="N41">
-        <v>89.81733334444441</v>
+        <v>88.9730484444444</v>
       </c>
       <c r="O41">
-        <v>21.55616000266666</v>
+        <v>21.35353162666665</v>
       </c>
       <c r="P41">
-        <v>68.26117334177775</v>
+        <v>67.61951681777775</v>
       </c>
       <c r="Q41">
-        <v>207.9611733417777</v>
+        <v>207.3195168177778</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09907548355497771</v>
+        <v>0.09981999237194195</v>
       </c>
       <c r="T41">
-        <v>0.7333570842917396</v>
+        <v>0.7436055283940809</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.727762331522743</v>
+        <v>3.634568273234675</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07852719542316516</v>
+        <v>0.07844902587779393</v>
       </c>
       <c r="C42">
-        <v>876.6623979090041</v>
+        <v>863.8277878146545</v>
       </c>
       <c r="D42">
-        <v>981.7823979090042</v>
+        <v>982.7207878146545</v>
       </c>
       <c r="E42">
-        <v>-630.48</v>
+        <v>-616.707</v>
       </c>
       <c r="F42">
-        <v>550.9200000000001</v>
+        <v>564.6930000000001</v>
       </c>
       <c r="G42">
         <v>445.8</v>
@@ -4731,28 +4731,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M42">
-        <v>33.771396</v>
+        <v>34.61568090000001</v>
       </c>
       <c r="N42">
-        <v>88.9730484444444</v>
+        <v>88.12876354444441</v>
       </c>
       <c r="O42">
-        <v>21.35353162666665</v>
+        <v>21.15090325066666</v>
       </c>
       <c r="P42">
-        <v>67.61951681777775</v>
+        <v>66.97786029377775</v>
       </c>
       <c r="Q42">
-        <v>207.3195168177778</v>
+        <v>206.6778602937777</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09981999237194195</v>
+        <v>0.1005897387759219</v>
       </c>
       <c r="T42">
-        <v>0.7436055283940809</v>
+        <v>0.754201377381247</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.634568273234675</v>
+        <v>3.545920266570414</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07844902587779393</v>
+        <v>0.0792646163324227</v>
       </c>
       <c r="C43">
-        <v>863.8277878146545</v>
+        <v>840.351403284345</v>
       </c>
       <c r="D43">
-        <v>982.7207878146545</v>
+        <v>973.0174032843451</v>
       </c>
       <c r="E43">
-        <v>-616.707</v>
+        <v>-602.934</v>
       </c>
       <c r="F43">
-        <v>564.6930000000001</v>
+        <v>578.4660000000001</v>
       </c>
       <c r="G43">
         <v>445.8</v>
@@ -4813,45 +4813,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M43">
-        <v>34.61568090000001</v>
+        <v>37.07967060000001</v>
       </c>
       <c r="N43">
-        <v>88.12876354444441</v>
+        <v>85.6647738444444</v>
       </c>
       <c r="O43">
-        <v>21.15090325066666</v>
+        <v>20.55954572266666</v>
       </c>
       <c r="P43">
-        <v>66.97786029377775</v>
+        <v>65.10522812177774</v>
       </c>
       <c r="Q43">
-        <v>206.6778602937777</v>
+        <v>204.8052281217777</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1005897387759219</v>
+        <v>0.1013860281593495</v>
       </c>
       <c r="T43">
-        <v>0.754201377381247</v>
+        <v>0.7651626004714192</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.545920266570414</v>
+        <v>3.310289505226737</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0792646163324227</v>
+        <v>0.07920772678705146</v>
       </c>
       <c r="C44">
-        <v>840.3514032843451</v>
+        <v>827.249018269813</v>
       </c>
       <c r="D44">
-        <v>973.0174032843451</v>
+        <v>973.688018269813</v>
       </c>
       <c r="E44">
-        <v>-602.9340000000001</v>
+        <v>-589.1610000000001</v>
       </c>
       <c r="F44">
-        <v>578.466</v>
+        <v>592.239</v>
       </c>
       <c r="G44">
         <v>445.8</v>
@@ -4895,28 +4895,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M44">
-        <v>37.0796706</v>
+        <v>37.9625199</v>
       </c>
       <c r="N44">
-        <v>85.66477384444441</v>
+        <v>84.78192454444441</v>
       </c>
       <c r="O44">
-        <v>20.55954572266666</v>
+        <v>20.34766189066666</v>
       </c>
       <c r="P44">
-        <v>65.10522812177776</v>
+        <v>64.43426265377775</v>
       </c>
       <c r="Q44">
-        <v>204.8052281217778</v>
+        <v>204.1342626537777</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1013860281593495</v>
+        <v>0.1022102575211429</v>
       </c>
       <c r="T44">
-        <v>0.765162600471419</v>
+        <v>0.7765084278805445</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.310289505226738</v>
+        <v>3.233306028360999</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07920772678705146</v>
+        <v>0.07915083724168023</v>
       </c>
       <c r="C45">
-        <v>827.249018269813</v>
+        <v>814.1475582842196</v>
       </c>
       <c r="D45">
-        <v>973.688018269813</v>
+        <v>974.3595582842197</v>
       </c>
       <c r="E45">
-        <v>-589.1610000000001</v>
+        <v>-575.388</v>
       </c>
       <c r="F45">
-        <v>592.239</v>
+        <v>606.0120000000001</v>
       </c>
       <c r="G45">
         <v>445.8</v>
@@ -4977,28 +4977,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M45">
-        <v>37.9625199</v>
+        <v>38.84536920000001</v>
       </c>
       <c r="N45">
-        <v>84.78192454444441</v>
+        <v>83.8990752444444</v>
       </c>
       <c r="O45">
-        <v>20.34766189066666</v>
+        <v>20.13577805866666</v>
       </c>
       <c r="P45">
-        <v>64.43426265377775</v>
+        <v>63.76329718577774</v>
       </c>
       <c r="Q45">
-        <v>204.1342626537777</v>
+        <v>203.4632971857777</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1022102575211429</v>
+        <v>0.1030639236458575</v>
       </c>
       <c r="T45">
-        <v>0.7765084278805445</v>
+        <v>0.7882594634114244</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.233306028360999</v>
+        <v>3.159821800443704</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07915083724168023</v>
+        <v>0.07909394769630899</v>
       </c>
       <c r="C46">
-        <v>814.1475582842196</v>
+        <v>801.0470252428272</v>
       </c>
       <c r="D46">
-        <v>974.3595582842197</v>
+        <v>975.0320252428272</v>
       </c>
       <c r="E46">
-        <v>-575.388</v>
+        <v>-561.615</v>
       </c>
       <c r="F46">
-        <v>606.0120000000001</v>
+        <v>619.7850000000001</v>
       </c>
       <c r="G46">
         <v>445.8</v>
@@ -5059,28 +5059,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M46">
-        <v>38.84536920000001</v>
+        <v>39.72821850000001</v>
       </c>
       <c r="N46">
-        <v>83.8990752444444</v>
+        <v>83.0162259444444</v>
       </c>
       <c r="O46">
-        <v>20.13577805866666</v>
+        <v>19.92389422666665</v>
       </c>
       <c r="P46">
-        <v>63.76329718577774</v>
+        <v>63.09233171777775</v>
       </c>
       <c r="Q46">
-        <v>203.4632971857777</v>
+        <v>202.7923317177777</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1030639236458575</v>
+        <v>0.1039486321751072</v>
       </c>
       <c r="T46">
-        <v>0.7882594634114244</v>
+        <v>0.8004378093252454</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.159821800443704</v>
+        <v>3.089603538211621</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07909394769630899</v>
+        <v>0.07903705815093776</v>
       </c>
       <c r="C47">
-        <v>801.0470252428272</v>
+        <v>787.9474210661889</v>
       </c>
       <c r="D47">
-        <v>975.0320252428272</v>
+        <v>975.7054210661889</v>
       </c>
       <c r="E47">
-        <v>-561.615</v>
+        <v>-547.842</v>
       </c>
       <c r="F47">
-        <v>619.7850000000001</v>
+        <v>633.5580000000001</v>
       </c>
       <c r="G47">
         <v>445.8</v>
@@ -5141,28 +5141,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M47">
-        <v>39.72821850000001</v>
+        <v>40.61106780000001</v>
       </c>
       <c r="N47">
-        <v>83.0162259444444</v>
+        <v>82.13337664444441</v>
       </c>
       <c r="O47">
-        <v>19.92389422666665</v>
+        <v>19.71201039466666</v>
       </c>
       <c r="P47">
-        <v>63.09233171777775</v>
+        <v>62.42136624977775</v>
       </c>
       <c r="Q47">
-        <v>202.7923317177777</v>
+        <v>202.1213662497777</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1039486321751072</v>
+        <v>0.1048661076869218</v>
       </c>
       <c r="T47">
-        <v>0.8004378093252454</v>
+        <v>0.8130672050877265</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.089603538211621</v>
+        <v>3.022438243902673</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07903705815093776</v>
+        <v>0.08176632860556653</v>
       </c>
       <c r="C48">
-        <v>787.9474210661889</v>
+        <v>742.8828062294024</v>
       </c>
       <c r="D48">
-        <v>975.7054210661889</v>
+        <v>944.4138062294024</v>
       </c>
       <c r="E48">
-        <v>-547.842</v>
+        <v>-534.069</v>
       </c>
       <c r="F48">
-        <v>633.5580000000001</v>
+        <v>647.3310000000001</v>
       </c>
       <c r="G48">
         <v>445.8</v>
@@ -5223,45 +5223,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M48">
-        <v>40.61106780000001</v>
+        <v>46.54309890000001</v>
       </c>
       <c r="N48">
-        <v>82.13337664444441</v>
+        <v>76.20134554444439</v>
       </c>
       <c r="O48">
-        <v>19.71201039466666</v>
+        <v>18.28832293066665</v>
       </c>
       <c r="P48">
-        <v>62.42136624977775</v>
+        <v>57.91302261377774</v>
       </c>
       <c r="Q48">
-        <v>202.1213662497777</v>
+        <v>197.6130226137777</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1048661076869218</v>
+        <v>0.1058182049161632</v>
       </c>
       <c r="T48">
-        <v>0.8130672050877265</v>
+        <v>0.8261731818223765</v>
       </c>
       <c r="U48">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.022438243902673</v>
+        <v>2.637221142239937</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08176632860556653</v>
+        <v>0.08176871906019528</v>
       </c>
       <c r="C49">
-        <v>742.8828062294024</v>
+        <v>729.0832789129835</v>
       </c>
       <c r="D49">
-        <v>944.4138062294024</v>
+        <v>944.3872789129836</v>
       </c>
       <c r="E49">
-        <v>-534.069</v>
+        <v>-520.2959999999999</v>
       </c>
       <c r="F49">
-        <v>647.3310000000001</v>
+        <v>661.1040000000002</v>
       </c>
       <c r="G49">
         <v>445.8</v>
@@ -5305,28 +5305,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M49">
-        <v>46.54309890000001</v>
+        <v>47.53337760000002</v>
       </c>
       <c r="N49">
-        <v>76.20134554444439</v>
+        <v>75.21106684444439</v>
       </c>
       <c r="O49">
-        <v>18.28832293066665</v>
+        <v>18.05065604266665</v>
       </c>
       <c r="P49">
-        <v>57.91302261377774</v>
+        <v>57.16041080177774</v>
       </c>
       <c r="Q49">
-        <v>197.6130226137777</v>
+        <v>196.8604108017777</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1058182049161632</v>
+        <v>0.1068069212696063</v>
       </c>
       <c r="T49">
-        <v>0.8261731818223765</v>
+        <v>0.8397832345852825</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.637221142239937</v>
+        <v>2.582279035109939</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08176871906019528</v>
+        <v>0.08177110951482405</v>
       </c>
       <c r="C50">
-        <v>729.0832789129836</v>
+        <v>715.2837530867561</v>
       </c>
       <c r="D50">
-        <v>944.3872789129836</v>
+        <v>944.3607530867562</v>
       </c>
       <c r="E50">
-        <v>-520.296</v>
+        <v>-506.523</v>
       </c>
       <c r="F50">
-        <v>661.104</v>
+        <v>674.8770000000001</v>
       </c>
       <c r="G50">
         <v>445.8</v>
@@ -5387,28 +5387,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M50">
-        <v>47.53337760000001</v>
+        <v>48.52365630000001</v>
       </c>
       <c r="N50">
-        <v>75.2110668444444</v>
+        <v>74.22078814444441</v>
       </c>
       <c r="O50">
-        <v>18.05065604266666</v>
+        <v>17.81298915466666</v>
       </c>
       <c r="P50">
-        <v>57.16041080177774</v>
+        <v>56.40779898977775</v>
       </c>
       <c r="Q50">
-        <v>196.8604108017777</v>
+        <v>196.1077989897777</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1068069212696063</v>
+        <v>0.1078344108133805</v>
       </c>
       <c r="T50">
-        <v>0.8397832345852825</v>
+        <v>0.853927014907518</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.582279035109939</v>
+        <v>2.529579462964838</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08177110951482405</v>
+        <v>0.08325549996945281</v>
       </c>
       <c r="C51">
-        <v>715.2837530867561</v>
+        <v>685.3219449189678</v>
       </c>
       <c r="D51">
-        <v>944.3607530867562</v>
+        <v>928.1719449189679</v>
       </c>
       <c r="E51">
-        <v>-506.523</v>
+        <v>-492.75</v>
       </c>
       <c r="F51">
-        <v>674.8770000000001</v>
+        <v>688.6500000000001</v>
       </c>
       <c r="G51">
         <v>445.8</v>
@@ -5469,45 +5469,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M51">
-        <v>48.52365630000001</v>
+        <v>52.19967000000001</v>
       </c>
       <c r="N51">
-        <v>74.22078814444441</v>
+        <v>70.5447744444444</v>
       </c>
       <c r="O51">
-        <v>17.81298915466666</v>
+        <v>16.93074586666665</v>
       </c>
       <c r="P51">
-        <v>56.40779898977775</v>
+        <v>53.61402857777774</v>
       </c>
       <c r="Q51">
-        <v>196.1077989897777</v>
+        <v>193.3140285777777</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1078344108133805</v>
+        <v>0.1089029999389056</v>
       </c>
       <c r="T51">
-        <v>0.853927014907518</v>
+        <v>0.868636546442643</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.529579462964838</v>
+        <v>2.351441004214095</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08325549996945281</v>
+        <v>0.08328753042408157</v>
       </c>
       <c r="C52">
-        <v>685.3219449189678</v>
+        <v>671.2057350909914</v>
       </c>
       <c r="D52">
-        <v>928.1719449189679</v>
+        <v>927.8287350909916</v>
       </c>
       <c r="E52">
-        <v>-492.75</v>
+        <v>-478.977</v>
       </c>
       <c r="F52">
-        <v>688.6500000000001</v>
+        <v>702.4230000000001</v>
       </c>
       <c r="G52">
         <v>445.8</v>
@@ -5551,28 +5551,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M52">
-        <v>52.19967000000001</v>
+        <v>53.24366340000001</v>
       </c>
       <c r="N52">
-        <v>70.5447744444444</v>
+        <v>69.50078104444441</v>
       </c>
       <c r="O52">
-        <v>16.93074586666665</v>
+        <v>16.68018745066666</v>
       </c>
       <c r="P52">
-        <v>53.61402857777774</v>
+        <v>52.82059359377775</v>
       </c>
       <c r="Q52">
-        <v>193.3140285777777</v>
+        <v>192.5205935937777</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1089029999389056</v>
+        <v>0.1100152049471053</v>
       </c>
       <c r="T52">
-        <v>0.868636546442643</v>
+        <v>0.8839464670200181</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.351441004214095</v>
+        <v>2.305334317856956</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08328753042408157</v>
+        <v>0.08331956087871036</v>
       </c>
       <c r="C53">
-        <v>671.2057350909914</v>
+        <v>657.0897789863609</v>
       </c>
       <c r="D53">
-        <v>927.8287350909916</v>
+        <v>927.4857789863611</v>
       </c>
       <c r="E53">
-        <v>-478.977</v>
+        <v>-465.204</v>
       </c>
       <c r="F53">
-        <v>702.4230000000001</v>
+        <v>716.1960000000001</v>
       </c>
       <c r="G53">
         <v>445.8</v>
@@ -5633,28 +5633,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M53">
-        <v>53.24366340000001</v>
+        <v>54.28765680000001</v>
       </c>
       <c r="N53">
-        <v>69.50078104444441</v>
+        <v>68.4567876444444</v>
       </c>
       <c r="O53">
-        <v>16.68018745066666</v>
+        <v>16.42962903466666</v>
       </c>
       <c r="P53">
-        <v>52.82059359377775</v>
+        <v>52.02715860977774</v>
       </c>
       <c r="Q53">
-        <v>192.5205935937777</v>
+        <v>191.7271586097777</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1100152049471053</v>
+        <v>0.1111737518306466</v>
       </c>
       <c r="T53">
-        <v>0.8839464670200181</v>
+        <v>0.8998943009547836</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.305334317856956</v>
+        <v>2.261000965590476</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08331956087871036</v>
+        <v>0.08335159133333912</v>
       </c>
       <c r="C54">
-        <v>657.0897789863609</v>
+        <v>642.9740763238273</v>
       </c>
       <c r="D54">
-        <v>927.4857789863611</v>
+        <v>927.1430763238275</v>
       </c>
       <c r="E54">
-        <v>-465.204</v>
+        <v>-451.4309999999999</v>
       </c>
       <c r="F54">
-        <v>716.1960000000001</v>
+        <v>729.9690000000002</v>
       </c>
       <c r="G54">
         <v>445.8</v>
@@ -5715,28 +5715,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M54">
-        <v>54.28765680000001</v>
+        <v>55.33165020000002</v>
       </c>
       <c r="N54">
-        <v>68.4567876444444</v>
+        <v>67.4127942444444</v>
       </c>
       <c r="O54">
-        <v>16.42962903466666</v>
+        <v>16.17907061866666</v>
       </c>
       <c r="P54">
-        <v>52.02715860977774</v>
+        <v>51.23372362577774</v>
       </c>
       <c r="Q54">
-        <v>191.7271586097777</v>
+        <v>190.9337236257777</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1111737518306466</v>
+        <v>0.1123815985815726</v>
       </c>
       <c r="T54">
-        <v>0.8998943009547836</v>
+        <v>0.9165207661208159</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.261000965590476</v>
+        <v>2.218340570013297</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08335159133333912</v>
+        <v>0.08338362178796788</v>
       </c>
       <c r="C55">
-        <v>642.9740763238273</v>
+        <v>628.8586268225563</v>
       </c>
       <c r="D55">
-        <v>927.1430763238275</v>
+        <v>926.8006268225564</v>
       </c>
       <c r="E55">
-        <v>-451.4309999999999</v>
+        <v>-437.6579999999999</v>
       </c>
       <c r="F55">
-        <v>729.9690000000002</v>
+        <v>743.7420000000002</v>
       </c>
       <c r="G55">
         <v>445.8</v>
@@ -5797,28 +5797,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M55">
-        <v>55.33165020000002</v>
+        <v>56.37564360000002</v>
       </c>
       <c r="N55">
-        <v>67.4127942444444</v>
+        <v>66.36880084444439</v>
       </c>
       <c r="O55">
-        <v>16.17907061866666</v>
+        <v>15.92851220266665</v>
       </c>
       <c r="P55">
-        <v>51.23372362577774</v>
+        <v>50.44028864177774</v>
       </c>
       <c r="Q55">
-        <v>190.9337236257777</v>
+        <v>190.1402886417777</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1123815985815726</v>
+        <v>0.1136419604086258</v>
       </c>
       <c r="T55">
-        <v>0.9165207661208159</v>
+        <v>0.9338701210766756</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.218340570013297</v>
+        <v>2.177260189087125</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08338362178796788</v>
+        <v>0.08341565224259664</v>
       </c>
       <c r="C56">
-        <v>628.8586268225563</v>
+        <v>614.7434302021283</v>
       </c>
       <c r="D56">
-        <v>926.8006268225564</v>
+        <v>926.4584302021285</v>
       </c>
       <c r="E56">
-        <v>-437.6579999999999</v>
+        <v>-423.8849999999999</v>
       </c>
       <c r="F56">
-        <v>743.7420000000002</v>
+        <v>757.5150000000002</v>
       </c>
       <c r="G56">
         <v>445.8</v>
@@ -5879,28 +5879,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M56">
-        <v>56.37564360000002</v>
+        <v>57.41963700000002</v>
       </c>
       <c r="N56">
-        <v>66.36880084444439</v>
+        <v>65.32480744444439</v>
       </c>
       <c r="O56">
-        <v>15.92851220266665</v>
+        <v>15.67795378666665</v>
       </c>
       <c r="P56">
-        <v>50.44028864177774</v>
+        <v>49.64685365777774</v>
       </c>
       <c r="Q56">
-        <v>190.1402886417777</v>
+        <v>189.3468536577777</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1136419604086258</v>
+        <v>0.1149583383168814</v>
       </c>
       <c r="T56">
-        <v>0.9338701210766756</v>
+        <v>0.951990558475018</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.177260189087125</v>
+        <v>2.137673640194632</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08341565224259664</v>
+        <v>0.08344768269722541</v>
       </c>
       <c r="C57">
-        <v>614.7434302021283</v>
+        <v>600.6284861825383</v>
       </c>
       <c r="D57">
-        <v>926.4584302021285</v>
+        <v>926.1164861825384</v>
       </c>
       <c r="E57">
-        <v>-423.8849999999999</v>
+        <v>-410.112</v>
       </c>
       <c r="F57">
-        <v>757.5150000000002</v>
+        <v>771.2880000000001</v>
       </c>
       <c r="G57">
         <v>445.8</v>
@@ -5961,28 +5961,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M57">
-        <v>57.41963700000002</v>
+        <v>58.46363040000001</v>
       </c>
       <c r="N57">
-        <v>65.32480744444439</v>
+        <v>64.2808140444444</v>
       </c>
       <c r="O57">
-        <v>15.67795378666665</v>
+        <v>15.42739537066666</v>
       </c>
       <c r="P57">
-        <v>49.64685365777774</v>
+        <v>48.85341867377774</v>
       </c>
       <c r="Q57">
-        <v>189.3468536577777</v>
+        <v>188.5534186737777</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1149583383168814</v>
+        <v>0.1163345515846032</v>
       </c>
       <c r="T57">
-        <v>0.951990558475018</v>
+        <v>0.9709346521187394</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.137673640194632</v>
+        <v>2.099500896619728</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08344768269722541</v>
+        <v>0.08347971315185418</v>
       </c>
       <c r="C58">
-        <v>600.6284861825383</v>
+        <v>586.513794484194</v>
       </c>
       <c r="D58">
-        <v>926.1164861825384</v>
+        <v>925.7747944841942</v>
       </c>
       <c r="E58">
-        <v>-410.112</v>
+        <v>-396.3389999999999</v>
       </c>
       <c r="F58">
-        <v>771.2880000000001</v>
+        <v>785.0610000000001</v>
       </c>
       <c r="G58">
         <v>445.8</v>
@@ -6043,28 +6043,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M58">
-        <v>58.46363040000001</v>
+        <v>59.50762380000002</v>
       </c>
       <c r="N58">
-        <v>64.2808140444444</v>
+        <v>63.23682064444439</v>
       </c>
       <c r="O58">
-        <v>15.42739537066666</v>
+        <v>15.17683695466665</v>
       </c>
       <c r="P58">
-        <v>48.85341867377774</v>
+        <v>48.05998368977774</v>
       </c>
       <c r="Q58">
-        <v>188.5534186737777</v>
+        <v>187.7599836897777</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1163345515846032</v>
+        <v>0.1177747747717539</v>
       </c>
       <c r="T58">
-        <v>0.9709346521187394</v>
+        <v>0.9907598663970528</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.099500896619728</v>
+        <v>2.062667547556224</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08347971315185418</v>
+        <v>0.08351174360648295</v>
       </c>
       <c r="C59">
-        <v>586.513794484194</v>
+        <v>572.3993548279162</v>
       </c>
       <c r="D59">
-        <v>925.7747944841942</v>
+        <v>925.4333548279163</v>
       </c>
       <c r="E59">
-        <v>-396.3389999999999</v>
+        <v>-382.5659999999999</v>
       </c>
       <c r="F59">
-        <v>785.0610000000001</v>
+        <v>798.8340000000002</v>
       </c>
       <c r="G59">
         <v>445.8</v>
@@ -6125,28 +6125,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M59">
-        <v>59.50762380000002</v>
+        <v>60.55161720000002</v>
       </c>
       <c r="N59">
-        <v>63.23682064444439</v>
+        <v>62.19282724444439</v>
       </c>
       <c r="O59">
-        <v>15.17683695466665</v>
+        <v>14.92627853866665</v>
       </c>
       <c r="P59">
-        <v>48.05998368977774</v>
+        <v>47.26654870577774</v>
       </c>
       <c r="Q59">
-        <v>187.7599836897777</v>
+        <v>186.9665487057777</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1177747747717539</v>
+        <v>0.1192835800154356</v>
       </c>
       <c r="T59">
-        <v>0.9907598663970528</v>
+        <v>1.011529138498143</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.062667547556224</v>
+        <v>2.027104313977668</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08351174360648295</v>
+        <v>0.0899110540611117</v>
       </c>
       <c r="C60">
-        <v>572.3993548279163</v>
+        <v>495.1156437063529</v>
       </c>
       <c r="D60">
-        <v>925.4333548279163</v>
+        <v>861.9226437063529</v>
       </c>
       <c r="E60">
-        <v>-382.566</v>
+        <v>-368.793</v>
       </c>
       <c r="F60">
-        <v>798.8340000000001</v>
+        <v>812.6070000000001</v>
       </c>
       <c r="G60">
         <v>445.8</v>
@@ -6207,45 +6207,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M60">
-        <v>60.55161720000001</v>
+        <v>73.13463</v>
       </c>
       <c r="N60">
-        <v>62.1928272444444</v>
+        <v>49.60981444444441</v>
       </c>
       <c r="O60">
-        <v>14.92627853866666</v>
+        <v>11.90635546666666</v>
       </c>
       <c r="P60">
-        <v>47.26654870577774</v>
+        <v>37.70345897777775</v>
       </c>
       <c r="Q60">
-        <v>186.9665487057777</v>
+        <v>177.4034589777777</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1192835800154356</v>
+        <v>0.1208659855149066</v>
       </c>
       <c r="T60">
-        <v>1.011529138498143</v>
+        <v>1.033311545823676</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.027104313977668</v>
+        <v>1.67833548135055</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0899110540611117</v>
+        <v>0.09005100451574047</v>
       </c>
       <c r="C61">
-        <v>495.1156437063529</v>
+        <v>480.0509488794582</v>
       </c>
       <c r="D61">
-        <v>861.9226437063529</v>
+        <v>860.6309488794584</v>
       </c>
       <c r="E61">
-        <v>-368.793</v>
+        <v>-355.02</v>
       </c>
       <c r="F61">
-        <v>812.6070000000001</v>
+        <v>826.3800000000001</v>
       </c>
       <c r="G61">
         <v>445.8</v>
@@ -6289,28 +6289,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M61">
-        <v>73.13463</v>
+        <v>74.3742</v>
       </c>
       <c r="N61">
-        <v>49.60981444444441</v>
+        <v>48.37024444444441</v>
       </c>
       <c r="O61">
-        <v>11.90635546666666</v>
+        <v>11.60885866666666</v>
       </c>
       <c r="P61">
-        <v>37.70345897777775</v>
+        <v>36.76138577777775</v>
       </c>
       <c r="Q61">
-        <v>177.4034589777777</v>
+        <v>176.4613857777777</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1208659855149066</v>
+        <v>0.1225275112893512</v>
       </c>
       <c r="T61">
-        <v>1.033311545823676</v>
+        <v>1.056183073515486</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.67833548135055</v>
+        <v>1.650363223328041</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09005100451574047</v>
+        <v>0.09019095497036922</v>
       </c>
       <c r="C62">
-        <v>480.0509488794582</v>
+        <v>464.9901197796522</v>
       </c>
       <c r="D62">
-        <v>860.6309488794584</v>
+        <v>859.3431197796524</v>
       </c>
       <c r="E62">
-        <v>-355.02</v>
+        <v>-341.247</v>
       </c>
       <c r="F62">
-        <v>826.3800000000001</v>
+        <v>840.1530000000001</v>
       </c>
       <c r="G62">
         <v>445.8</v>
@@ -6371,28 +6371,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M62">
-        <v>74.3742</v>
+        <v>75.61377</v>
       </c>
       <c r="N62">
-        <v>48.37024444444441</v>
+        <v>47.13067444444441</v>
       </c>
       <c r="O62">
-        <v>11.60885866666666</v>
+        <v>11.31136186666666</v>
       </c>
       <c r="P62">
-        <v>36.76138577777775</v>
+        <v>35.81931257777775</v>
       </c>
       <c r="Q62">
-        <v>176.4613857777777</v>
+        <v>175.5193125777777</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1225275112893512</v>
+        <v>0.1242742435137673</v>
       </c>
       <c r="T62">
-        <v>1.056183073515486</v>
+        <v>1.080227500063287</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.650363223328041</v>
+        <v>1.623308088519385</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09019095497036922</v>
+        <v>0.090330905424998</v>
       </c>
       <c r="C63">
-        <v>464.9901197796522</v>
+        <v>449.9331390790983</v>
       </c>
       <c r="D63">
-        <v>859.3431197796524</v>
+        <v>858.0591390790984</v>
       </c>
       <c r="E63">
-        <v>-341.247</v>
+        <v>-327.4739999999999</v>
       </c>
       <c r="F63">
-        <v>840.1530000000001</v>
+        <v>853.9260000000002</v>
       </c>
       <c r="G63">
         <v>445.8</v>
@@ -6453,28 +6453,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M63">
-        <v>75.61377</v>
+        <v>76.85334000000002</v>
       </c>
       <c r="N63">
-        <v>47.13067444444441</v>
+        <v>45.89110444444439</v>
       </c>
       <c r="O63">
-        <v>11.31136186666666</v>
+        <v>11.01386506666665</v>
       </c>
       <c r="P63">
-        <v>35.81931257777775</v>
+        <v>34.87723937777774</v>
       </c>
       <c r="Q63">
-        <v>175.5193125777777</v>
+        <v>174.5772393777777</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1242742435137673</v>
+        <v>0.1261129090131526</v>
       </c>
       <c r="T63">
-        <v>1.080227500063287</v>
+        <v>1.105537422745182</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.623308088519385</v>
+        <v>1.597125699994878</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.090330905424998</v>
+        <v>0.09047085587962676</v>
       </c>
       <c r="C64">
-        <v>449.9331390790983</v>
+        <v>434.8799895533668</v>
       </c>
       <c r="D64">
-        <v>858.0591390790984</v>
+        <v>856.7789895533668</v>
       </c>
       <c r="E64">
-        <v>-327.4739999999999</v>
+        <v>-313.701</v>
       </c>
       <c r="F64">
-        <v>853.9260000000002</v>
+        <v>867.6990000000001</v>
       </c>
       <c r="G64">
         <v>445.8</v>
@@ -6535,28 +6535,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M64">
-        <v>76.85334000000002</v>
+        <v>78.09291</v>
       </c>
       <c r="N64">
-        <v>45.89110444444439</v>
+        <v>44.65153444444441</v>
       </c>
       <c r="O64">
-        <v>11.01386506666665</v>
+        <v>10.71636826666666</v>
       </c>
       <c r="P64">
-        <v>34.87723937777774</v>
+        <v>33.93516617777775</v>
       </c>
       <c r="Q64">
-        <v>174.5772393777777</v>
+        <v>173.6351661777777</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1261129090131526</v>
+        <v>0.1280509618368291</v>
       </c>
       <c r="T64">
-        <v>1.105537422745182</v>
+        <v>1.132215449355828</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.597125699994878</v>
+        <v>1.571774498407658</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09047085587962676</v>
+        <v>0.09061080633425553</v>
       </c>
       <c r="C65">
-        <v>434.8799895533668</v>
+        <v>419.830654080664</v>
       </c>
       <c r="D65">
-        <v>856.7789895533668</v>
+        <v>855.502654080664</v>
       </c>
       <c r="E65">
-        <v>-313.701</v>
+        <v>-299.928</v>
       </c>
       <c r="F65">
-        <v>867.6990000000001</v>
+        <v>881.4720000000001</v>
       </c>
       <c r="G65">
         <v>445.8</v>
@@ -6617,28 +6617,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M65">
-        <v>78.09291</v>
+        <v>79.33248</v>
       </c>
       <c r="N65">
-        <v>44.65153444444441</v>
+        <v>43.41196444444441</v>
       </c>
       <c r="O65">
-        <v>10.71636826666666</v>
+        <v>10.41887146666666</v>
       </c>
       <c r="P65">
-        <v>33.93516617777775</v>
+        <v>32.99309297777775</v>
       </c>
       <c r="Q65">
-        <v>173.6351661777777</v>
+        <v>172.6930929777777</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1280509618368291</v>
+        <v>0.1300966842618209</v>
       </c>
       <c r="T65">
-        <v>1.132215449355828</v>
+        <v>1.160375588555955</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.571774498407658</v>
+        <v>1.547215521870039</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09061080633425553</v>
+        <v>0.09075075678888431</v>
       </c>
       <c r="C66">
-        <v>419.830654080664</v>
+        <v>404.7851156410691</v>
       </c>
       <c r="D66">
-        <v>855.502654080664</v>
+        <v>854.2301156410692</v>
       </c>
       <c r="E66">
-        <v>-299.928</v>
+        <v>-286.155</v>
       </c>
       <c r="F66">
-        <v>881.4720000000001</v>
+        <v>895.2450000000001</v>
       </c>
       <c r="G66">
         <v>445.8</v>
@@ -6699,28 +6699,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M66">
-        <v>79.33248</v>
+        <v>80.57205</v>
       </c>
       <c r="N66">
-        <v>43.41196444444441</v>
+        <v>42.17239444444441</v>
       </c>
       <c r="O66">
-        <v>10.41887146666666</v>
+        <v>10.12137466666666</v>
       </c>
       <c r="P66">
-        <v>32.99309297777775</v>
+        <v>32.05101977777775</v>
       </c>
       <c r="Q66">
-        <v>172.6930929777777</v>
+        <v>171.7510197777777</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1300966842618209</v>
+        <v>0.132259305111098</v>
       </c>
       <c r="T66">
-        <v>1.160375588555955</v>
+        <v>1.190144878567518</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.547215521870039</v>
+        <v>1.523412206148961</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09075075678888431</v>
+        <v>0.09089070724351306</v>
       </c>
       <c r="C67">
-        <v>404.7851156410691</v>
+        <v>389.7433573157786</v>
       </c>
       <c r="D67">
-        <v>854.2301156410692</v>
+        <v>852.9613573157787</v>
       </c>
       <c r="E67">
-        <v>-286.155</v>
+        <v>-272.3819999999999</v>
       </c>
       <c r="F67">
-        <v>895.2450000000001</v>
+        <v>909.0180000000001</v>
       </c>
       <c r="G67">
         <v>445.8</v>
@@ -6781,28 +6781,28 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M67">
-        <v>80.57205</v>
+        <v>81.81162</v>
       </c>
       <c r="N67">
-        <v>42.17239444444441</v>
+        <v>40.93282444444441</v>
       </c>
       <c r="O67">
-        <v>10.12137466666666</v>
+        <v>9.823877866666658</v>
       </c>
       <c r="P67">
-        <v>32.05101977777775</v>
+        <v>31.10894657777775</v>
       </c>
       <c r="Q67">
-        <v>171.7510197777777</v>
+        <v>170.8089465777777</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.132259305111098</v>
+        <v>0.134549138951509</v>
       </c>
       <c r="T67">
-        <v>1.190144878567518</v>
+        <v>1.221665303285642</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.523412206148961</v>
+        <v>1.500330203025492</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09089070724351306</v>
+        <v>0.1227113582332347</v>
       </c>
       <c r="C68">
-        <v>389.7433573157786</v>
+        <v>160.6389119710291</v>
       </c>
       <c r="D68">
-        <v>852.9613573157787</v>
+        <v>637.6299119710293</v>
       </c>
       <c r="E68">
-        <v>-272.3819999999999</v>
+        <v>-258.6089999999999</v>
       </c>
       <c r="F68">
-        <v>909.0180000000001</v>
+        <v>922.7910000000002</v>
       </c>
       <c r="G68">
         <v>445.8</v>
@@ -6863,45 +6863,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M68">
-        <v>81.81162</v>
+        <v>135.4657188</v>
       </c>
       <c r="N68">
-        <v>40.93282444444441</v>
+        <v>-12.72127435555564</v>
       </c>
       <c r="O68">
-        <v>9.823877866666658</v>
+        <v>-3.053105845333353</v>
       </c>
       <c r="P68">
-        <v>31.10894657777775</v>
+        <v>-9.668168510222284</v>
       </c>
       <c r="Q68">
-        <v>170.8089465777777</v>
+        <v>130.0318314897777</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.134549138951509</v>
+        <v>0.1386183806289882</v>
       </c>
       <c r="T68">
-        <v>1.221665303285642</v>
+        <v>1.277679946658988</v>
       </c>
       <c r="U68">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.24</v>
+        <v>0.2174621515142076</v>
       </c>
       <c r="W68">
-        <v>0.0684</v>
+        <v>0.1148765561577143</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y68">
-        <v>1.500330203025492</v>
+        <v>0.9060922979758652</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1227113582332347</v>
+        <v>0.1237213582332347</v>
       </c>
       <c r="C69">
-        <v>160.6389119710291</v>
+        <v>141.7972538480927</v>
       </c>
       <c r="D69">
-        <v>637.6299119710293</v>
+        <v>632.561253848093</v>
       </c>
       <c r="E69">
-        <v>-258.6089999999999</v>
+        <v>-244.8359999999999</v>
       </c>
       <c r="F69">
-        <v>922.7910000000002</v>
+        <v>936.5640000000002</v>
       </c>
       <c r="G69">
         <v>445.8</v>
@@ -6945,37 +6945,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M69">
-        <v>135.4657188</v>
+        <v>137.4875952</v>
       </c>
       <c r="N69">
-        <v>-12.72127435555564</v>
+        <v>-14.74315075555563</v>
       </c>
       <c r="O69">
-        <v>-3.053105845333353</v>
+        <v>-3.538356181333352</v>
       </c>
       <c r="P69">
-        <v>-9.668168510222284</v>
+        <v>-11.20479457422228</v>
       </c>
       <c r="Q69">
-        <v>130.0318314897777</v>
+        <v>128.4952054257777</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1386183806289882</v>
+        <v>0.1415189550236441</v>
       </c>
       <c r="T69">
-        <v>1.277679946658988</v>
+        <v>1.317607444992081</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2174621515142076</v>
+        <v>0.2142641786978222</v>
       </c>
       <c r="W69">
-        <v>0.1148765561577143</v>
+        <v>0.1153460185671597</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9060922979758652</v>
+        <v>0.8927674112409261</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1237213582332347</v>
+        <v>0.1247313582332347</v>
       </c>
       <c r="C70">
-        <v>141.7972538480927</v>
+        <v>123.0355439197308</v>
       </c>
       <c r="D70">
-        <v>632.561253848093</v>
+        <v>627.5725439197311</v>
       </c>
       <c r="E70">
-        <v>-244.8359999999999</v>
+        <v>-231.0629999999999</v>
       </c>
       <c r="F70">
-        <v>936.5640000000002</v>
+        <v>950.3370000000002</v>
       </c>
       <c r="G70">
         <v>445.8</v>
@@ -7027,37 +7027,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M70">
-        <v>137.4875952</v>
+        <v>139.5094716</v>
       </c>
       <c r="N70">
-        <v>-14.74315075555563</v>
+        <v>-16.76502715555563</v>
       </c>
       <c r="O70">
-        <v>-3.538356181333352</v>
+        <v>-4.02360651733335</v>
       </c>
       <c r="P70">
-        <v>-11.20479457422228</v>
+        <v>-12.74142063822228</v>
       </c>
       <c r="Q70">
-        <v>128.4952054257777</v>
+        <v>126.9585793617777</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1415189550236441</v>
+        <v>0.1446066632502133</v>
       </c>
       <c r="T70">
-        <v>1.317607444992081</v>
+        <v>1.360110910959567</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2142641786978222</v>
+        <v>0.2111589007456799</v>
       </c>
       <c r="W70">
-        <v>0.1153460185671597</v>
+        <v>0.1158018733705342</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8927674112409261</v>
+        <v>0.8798287531069996</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1247313582332347</v>
+        <v>0.1257413582332347</v>
       </c>
       <c r="C71">
-        <v>123.0355439197308</v>
+        <v>104.3519054466691</v>
       </c>
       <c r="D71">
-        <v>627.5725439197311</v>
+        <v>622.6619054466693</v>
       </c>
       <c r="E71">
-        <v>-231.0629999999999</v>
+        <v>-217.2899999999998</v>
       </c>
       <c r="F71">
-        <v>950.3370000000002</v>
+        <v>964.1100000000002</v>
       </c>
       <c r="G71">
         <v>445.8</v>
@@ -7109,37 +7109,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M71">
-        <v>139.5094716</v>
+        <v>141.531348</v>
       </c>
       <c r="N71">
-        <v>-16.76502715555563</v>
+        <v>-18.78690355555563</v>
       </c>
       <c r="O71">
-        <v>-4.02360651733335</v>
+        <v>-4.50885685333335</v>
       </c>
       <c r="P71">
-        <v>-12.74142063822228</v>
+        <v>-14.27804670222228</v>
       </c>
       <c r="Q71">
-        <v>126.9585793617777</v>
+        <v>125.4219532977777</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1446066632502133</v>
+        <v>0.147900218691887</v>
       </c>
       <c r="T71">
-        <v>1.360110910959567</v>
+        <v>1.405447941324887</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2111589007456799</v>
+        <v>0.2081423450207416</v>
       </c>
       <c r="W71">
-        <v>0.1158018733705342</v>
+        <v>0.1162447037509552</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8798287531069996</v>
+        <v>0.8672597709197568</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1257413582332347</v>
+        <v>0.1267513582332347</v>
       </c>
       <c r="C72">
-        <v>104.3519054466691</v>
+        <v>85.74451997411188</v>
       </c>
       <c r="D72">
-        <v>622.6619054466693</v>
+        <v>617.8275199741121</v>
       </c>
       <c r="E72">
-        <v>-217.2899999999998</v>
+        <v>-203.5169999999998</v>
       </c>
       <c r="F72">
-        <v>964.1100000000002</v>
+        <v>977.8830000000003</v>
       </c>
       <c r="G72">
         <v>445.8</v>
@@ -7191,37 +7191,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M72">
-        <v>141.531348</v>
+        <v>143.5532244000001</v>
       </c>
       <c r="N72">
-        <v>-18.78690355555563</v>
+        <v>-20.80877995555565</v>
       </c>
       <c r="O72">
-        <v>-4.50885685333335</v>
+        <v>-4.994107189333356</v>
       </c>
       <c r="P72">
-        <v>-14.27804670222228</v>
+        <v>-15.81467276622229</v>
       </c>
       <c r="Q72">
-        <v>125.4219532977777</v>
+        <v>123.8853272337777</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.147900218691887</v>
+        <v>0.151420915888159</v>
       </c>
       <c r="T72">
-        <v>1.405447941324887</v>
+        <v>1.453911663439538</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2081423450207416</v>
+        <v>0.2052107626965058</v>
       </c>
       <c r="W72">
-        <v>0.1162447037509552</v>
+        <v>0.116675060036153</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8672597709197568</v>
+        <v>0.8550448445687742</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1267513582332347</v>
+        <v>0.1277613582332347</v>
       </c>
       <c r="C73">
-        <v>85.74451997411211</v>
+        <v>67.21162508655277</v>
       </c>
       <c r="D73">
-        <v>617.8275199741121</v>
+        <v>613.0676250865529</v>
       </c>
       <c r="E73">
-        <v>-203.5170000000001</v>
+        <v>-189.744</v>
       </c>
       <c r="F73">
-        <v>977.883</v>
+        <v>991.6560000000001</v>
       </c>
       <c r="G73">
         <v>445.8</v>
@@ -7273,37 +7273,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M73">
-        <v>143.5532244</v>
+        <v>145.5751008</v>
       </c>
       <c r="N73">
-        <v>-20.80877995555562</v>
+        <v>-22.83065635555562</v>
       </c>
       <c r="O73">
-        <v>-4.994107189333349</v>
+        <v>-5.479357525333348</v>
       </c>
       <c r="P73">
-        <v>-15.81467276622227</v>
+        <v>-17.35129883022227</v>
       </c>
       <c r="Q73">
-        <v>123.8853272337777</v>
+        <v>122.3487011697777</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.151420915888159</v>
+        <v>0.1551930914555932</v>
       </c>
       <c r="T73">
-        <v>1.453911663439537</v>
+        <v>1.50583707999095</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2052107626965058</v>
+        <v>0.2023606132146099</v>
       </c>
       <c r="W73">
-        <v>0.116675060036153</v>
+        <v>0.1170934619800953</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8550448445687744</v>
+        <v>0.8431692217275414</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1277613582332347</v>
+        <v>0.1287713582332347</v>
       </c>
       <c r="C74">
-        <v>67.21162508655277</v>
+        <v>48.751512265575</v>
       </c>
       <c r="D74">
-        <v>613.0676250865529</v>
+        <v>608.380512265575</v>
       </c>
       <c r="E74">
-        <v>-189.744</v>
+        <v>-175.971</v>
       </c>
       <c r="F74">
-        <v>991.6560000000001</v>
+        <v>1005.429</v>
       </c>
       <c r="G74">
         <v>445.8</v>
@@ -7355,37 +7355,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M74">
-        <v>145.5751008</v>
+        <v>147.5969772</v>
       </c>
       <c r="N74">
-        <v>-22.83065635555562</v>
+        <v>-24.85253275555561</v>
       </c>
       <c r="O74">
-        <v>-5.479357525333348</v>
+        <v>-5.964607861333347</v>
       </c>
       <c r="P74">
-        <v>-17.35129883022227</v>
+        <v>-18.88792489422227</v>
       </c>
       <c r="Q74">
-        <v>122.3487011697777</v>
+        <v>120.8120751057777</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1551930914555932</v>
+        <v>0.15924468743543</v>
       </c>
       <c r="T74">
-        <v>1.50583707999095</v>
+        <v>1.561608823694318</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2023606132146099</v>
+        <v>0.1995885500198893</v>
       </c>
       <c r="W74">
-        <v>0.1170934619800953</v>
+        <v>0.1175004008570803</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8431692217275414</v>
+        <v>0.8316189584162053</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1287713582332347</v>
+        <v>0.1297813582332347</v>
       </c>
       <c r="C75">
-        <v>48.751512265575</v>
+        <v>30.36252484517593</v>
       </c>
       <c r="D75">
-        <v>608.380512265575</v>
+        <v>603.7645248451761</v>
       </c>
       <c r="E75">
-        <v>-175.971</v>
+        <v>-162.198</v>
       </c>
       <c r="F75">
-        <v>1005.429</v>
+        <v>1019.202</v>
       </c>
       <c r="G75">
         <v>445.8</v>
@@ -7437,37 +7437,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M75">
-        <v>147.5969772</v>
+        <v>149.6188536</v>
       </c>
       <c r="N75">
-        <v>-24.85253275555561</v>
+        <v>-26.87440915555561</v>
       </c>
       <c r="O75">
-        <v>-5.964607861333347</v>
+        <v>-6.449858197333346</v>
       </c>
       <c r="P75">
-        <v>-18.88792489422227</v>
+        <v>-20.42455095822227</v>
       </c>
       <c r="Q75">
-        <v>120.8120751057777</v>
+        <v>119.2754490417777</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.15924468743543</v>
+        <v>0.163607944644485</v>
       </c>
       <c r="T75">
-        <v>1.561608823694318</v>
+        <v>1.621670701528715</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1995885500198893</v>
+        <v>0.1968914074520529</v>
       </c>
       <c r="W75">
-        <v>0.1175004008570803</v>
+        <v>0.1178963413860386</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8316189584162053</v>
+        <v>0.8203808643835538</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1297813582332347</v>
+        <v>0.1307913582332347</v>
       </c>
       <c r="C76">
-        <v>30.36252484517593</v>
+        <v>12.04305605947138</v>
       </c>
       <c r="D76">
-        <v>603.7645248451761</v>
+        <v>599.2180560594716</v>
       </c>
       <c r="E76">
-        <v>-162.198</v>
+        <v>-148.425</v>
       </c>
       <c r="F76">
-        <v>1019.202</v>
+        <v>1032.975</v>
       </c>
       <c r="G76">
         <v>445.8</v>
@@ -7519,37 +7519,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M76">
-        <v>149.6188536</v>
+        <v>151.64073</v>
       </c>
       <c r="N76">
-        <v>-26.87440915555561</v>
+        <v>-28.89628555555564</v>
       </c>
       <c r="O76">
-        <v>-6.449858197333346</v>
+        <v>-6.935108533333352</v>
       </c>
       <c r="P76">
-        <v>-20.42455095822227</v>
+        <v>-21.96117702222228</v>
       </c>
       <c r="Q76">
-        <v>119.2754490417777</v>
+        <v>117.7388229777777</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.163607944644485</v>
+        <v>0.1683202624302645</v>
       </c>
       <c r="T76">
-        <v>1.621670701528715</v>
+        <v>1.686537529589864</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1968914074520529</v>
+        <v>0.1942661886860255</v>
       </c>
       <c r="W76">
-        <v>0.1178963413860386</v>
+        <v>0.1182817235008915</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8203808643835538</v>
+        <v>0.8094424528584396</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1307913582332347</v>
+        <v>0.1742461950262836</v>
       </c>
       <c r="C77">
-        <v>12.04305605947138</v>
+        <v>-148.3608684453934</v>
       </c>
       <c r="D77">
-        <v>599.2180560594716</v>
+        <v>452.5871315546067</v>
       </c>
       <c r="E77">
-        <v>-148.425</v>
+        <v>-134.652</v>
       </c>
       <c r="F77">
-        <v>1032.975</v>
+        <v>1046.748</v>
       </c>
       <c r="G77">
         <v>445.8</v>
@@ -7601,45 +7601,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M77">
-        <v>151.64073</v>
+        <v>210.1869984</v>
       </c>
       <c r="N77">
-        <v>-28.89628555555564</v>
+        <v>-87.44255395555561</v>
       </c>
       <c r="O77">
-        <v>-6.935108533333352</v>
+        <v>-20.98621294933335</v>
       </c>
       <c r="P77">
-        <v>-21.96117702222228</v>
+        <v>-66.45634100622226</v>
       </c>
       <c r="Q77">
-        <v>117.7388229777777</v>
+        <v>73.24365899377773</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1683202624302645</v>
+        <v>0.1792787600025625</v>
       </c>
       <c r="T77">
-        <v>1.686537529589864</v>
+        <v>1.837385373505636</v>
       </c>
       <c r="U77">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1942661886860255</v>
+        <v>0.140154561846898</v>
       </c>
       <c r="W77">
-        <v>0.1182817235008915</v>
+        <v>0.1726569639811429</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8094424528584396</v>
+        <v>0.5839773410287418</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1742461950262836</v>
+        <v>0.1757961950262836</v>
       </c>
       <c r="C78">
-        <v>-148.3608684453934</v>
+        <v>-166.0500445488331</v>
       </c>
       <c r="D78">
-        <v>452.5871315546067</v>
+        <v>448.6709554511672</v>
       </c>
       <c r="E78">
-        <v>-134.652</v>
+        <v>-120.8789999999999</v>
       </c>
       <c r="F78">
-        <v>1046.748</v>
+        <v>1060.521</v>
       </c>
       <c r="G78">
         <v>445.8</v>
@@ -7683,37 +7683,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M78">
-        <v>210.1869984</v>
+        <v>212.9526168</v>
       </c>
       <c r="N78">
-        <v>-87.44255395555561</v>
+        <v>-90.20817235555563</v>
       </c>
       <c r="O78">
-        <v>-20.98621294933335</v>
+        <v>-21.64996136533335</v>
       </c>
       <c r="P78">
-        <v>-66.45634100622226</v>
+        <v>-68.55821099022228</v>
       </c>
       <c r="Q78">
-        <v>73.24365899377773</v>
+        <v>71.14178900977771</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1792787600025625</v>
+        <v>0.1850821843505</v>
       </c>
       <c r="T78">
-        <v>1.837385373505636</v>
+        <v>1.917271694092838</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.140154561846898</v>
+        <v>0.1383343727320032</v>
       </c>
       <c r="W78">
-        <v>0.1726569639811429</v>
+        <v>0.1730224579554138</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5839773410287418</v>
+        <v>0.5763932197166801</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1757961950262836</v>
+        <v>0.1773461950262836</v>
       </c>
       <c r="C79">
-        <v>-166.0500445488331</v>
+        <v>-183.6720297469017</v>
       </c>
       <c r="D79">
-        <v>448.6709554511672</v>
+        <v>444.8219702530984</v>
       </c>
       <c r="E79">
-        <v>-120.8789999999999</v>
+        <v>-107.106</v>
       </c>
       <c r="F79">
-        <v>1060.521</v>
+        <v>1074.294</v>
       </c>
       <c r="G79">
         <v>445.8</v>
@@ -7765,37 +7765,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M79">
-        <v>212.9526168</v>
+        <v>215.7182352</v>
       </c>
       <c r="N79">
-        <v>-90.20817235555563</v>
+        <v>-92.97379075555563</v>
       </c>
       <c r="O79">
-        <v>-21.64996136533335</v>
+        <v>-22.31370978133335</v>
       </c>
       <c r="P79">
-        <v>-68.55821099022228</v>
+        <v>-70.66008097422227</v>
       </c>
       <c r="Q79">
-        <v>71.14178900977771</v>
+        <v>69.03991902577772</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1850821843505</v>
+        <v>0.1914131927300682</v>
       </c>
       <c r="T79">
-        <v>1.917271694092838</v>
+        <v>2.004420407460695</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1383343727320032</v>
+        <v>0.136560855132875</v>
       </c>
       <c r="W79">
-        <v>0.1730224579554138</v>
+        <v>0.1733785802893187</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5763932197166801</v>
+        <v>0.5690035630536459</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1773461950262836</v>
+        <v>0.1788961950262836</v>
       </c>
       <c r="C80">
-        <v>-183.6720297469017</v>
+        <v>-201.228538550566</v>
       </c>
       <c r="D80">
-        <v>444.8219702530984</v>
+        <v>441.0384614494342</v>
       </c>
       <c r="E80">
-        <v>-107.106</v>
+        <v>-93.33299999999986</v>
       </c>
       <c r="F80">
-        <v>1074.294</v>
+        <v>1088.067</v>
       </c>
       <c r="G80">
         <v>445.8</v>
@@ -7847,37 +7847,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M80">
-        <v>215.7182352</v>
+        <v>218.4838536000001</v>
       </c>
       <c r="N80">
-        <v>-92.97379075555563</v>
+        <v>-95.73940915555565</v>
       </c>
       <c r="O80">
-        <v>-22.31370978133335</v>
+        <v>-22.97745819733336</v>
       </c>
       <c r="P80">
-        <v>-70.66008097422227</v>
+        <v>-72.76195095822229</v>
       </c>
       <c r="Q80">
-        <v>69.03991902577772</v>
+        <v>66.9380490417777</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1914131927300682</v>
+        <v>0.1983471542886429</v>
       </c>
       <c r="T80">
-        <v>2.004420407460695</v>
+        <v>2.099868998292157</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.136560855132875</v>
+        <v>0.1348322367134715</v>
       </c>
       <c r="W80">
-        <v>0.1733785802893187</v>
+        <v>0.1737256868679349</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5690035630536459</v>
+        <v>0.5618009863061313</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1788961950262836</v>
+        <v>0.1804461950262836</v>
       </c>
       <c r="C81">
-        <v>-201.228538550566</v>
+        <v>-218.7212276305052</v>
       </c>
       <c r="D81">
-        <v>441.0384614494342</v>
+        <v>437.318772369495</v>
       </c>
       <c r="E81">
-        <v>-93.33299999999986</v>
+        <v>-79.55999999999995</v>
       </c>
       <c r="F81">
-        <v>1088.067</v>
+        <v>1101.84</v>
       </c>
       <c r="G81">
         <v>445.8</v>
@@ -7929,37 +7929,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M81">
-        <v>218.4838536000001</v>
+        <v>221.249472</v>
       </c>
       <c r="N81">
-        <v>-95.73940915555565</v>
+        <v>-98.50502755555561</v>
       </c>
       <c r="O81">
-        <v>-22.97745819733336</v>
+        <v>-23.64120661333335</v>
       </c>
       <c r="P81">
-        <v>-72.76195095822229</v>
+        <v>-74.86382094222228</v>
       </c>
       <c r="Q81">
-        <v>66.9380490417777</v>
+        <v>64.83617905777771</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1983471542886429</v>
+        <v>0.205974512003075</v>
       </c>
       <c r="T81">
-        <v>2.099868998292157</v>
+        <v>2.204862448206764</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1348322367134715</v>
+        <v>0.1331468337545531</v>
       </c>
       <c r="W81">
-        <v>0.1737256868679349</v>
+        <v>0.1740641157820857</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5618009863061313</v>
+        <v>0.5547784739773047</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1804461950262836</v>
+        <v>0.1819961950262836</v>
       </c>
       <c r="C82">
-        <v>-218.7212276305052</v>
+        <v>-236.1516982358203</v>
       </c>
       <c r="D82">
-        <v>437.318772369495</v>
+        <v>433.6613017641801</v>
       </c>
       <c r="E82">
-        <v>-79.55999999999995</v>
+        <v>-65.78699999999981</v>
       </c>
       <c r="F82">
-        <v>1101.84</v>
+        <v>1115.613</v>
       </c>
       <c r="G82">
         <v>445.8</v>
@@ -8011,37 +8011,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M82">
-        <v>221.249472</v>
+        <v>224.0150904000001</v>
       </c>
       <c r="N82">
-        <v>-98.50502755555561</v>
+        <v>-101.2706459555557</v>
       </c>
       <c r="O82">
-        <v>-23.64120661333335</v>
+        <v>-24.30495502933336</v>
       </c>
       <c r="P82">
-        <v>-74.86382094222228</v>
+        <v>-76.96569092622231</v>
       </c>
       <c r="Q82">
-        <v>64.83617905777771</v>
+        <v>62.73430907377768</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.205974512003075</v>
+        <v>0.2144047494769211</v>
       </c>
       <c r="T82">
-        <v>2.204862448206764</v>
+        <v>2.320907840217647</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1331468337545531</v>
+        <v>0.1315030456835092</v>
       </c>
       <c r="W82">
-        <v>0.1740641157820857</v>
+        <v>0.1743941884267514</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5547784739773047</v>
+        <v>0.5479293570146218</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1819961950262836</v>
+        <v>0.1835461950262836</v>
       </c>
       <c r="C83">
-        <v>-236.1516982358203</v>
+        <v>-253.5214984923718</v>
       </c>
       <c r="D83">
-        <v>433.6613017641801</v>
+        <v>430.0645015076284</v>
       </c>
       <c r="E83">
-        <v>-65.78699999999981</v>
+        <v>-52.0139999999999</v>
       </c>
       <c r="F83">
-        <v>1115.613</v>
+        <v>1129.386</v>
       </c>
       <c r="G83">
         <v>445.8</v>
@@ -8093,37 +8093,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M83">
-        <v>224.0150904000001</v>
+        <v>226.7807088</v>
       </c>
       <c r="N83">
-        <v>-101.2706459555557</v>
+        <v>-104.0362643555556</v>
       </c>
       <c r="O83">
-        <v>-24.30495502933336</v>
+        <v>-24.96870344533335</v>
       </c>
       <c r="P83">
-        <v>-76.96569092622231</v>
+        <v>-79.06756091022228</v>
       </c>
       <c r="Q83">
-        <v>62.73430907377768</v>
+        <v>60.63243908977771</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2144047494769211</v>
+        <v>0.2237716800034167</v>
       </c>
       <c r="T83">
-        <v>2.320907840217647</v>
+        <v>2.449847164674182</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1315030456835092</v>
+        <v>0.1298993500044421</v>
       </c>
       <c r="W83">
-        <v>0.1743941884267514</v>
+        <v>0.174716210519108</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5479293570146218</v>
+        <v>0.5412472916851753</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1835461950262836</v>
+        <v>0.1850961950262836</v>
       </c>
       <c r="C84">
-        <v>-253.5214984923718</v>
+        <v>-270.8321255876912</v>
       </c>
       <c r="D84">
-        <v>430.0645015076284</v>
+        <v>426.5268744123092</v>
       </c>
       <c r="E84">
-        <v>-52.0139999999999</v>
+        <v>-38.24099999999976</v>
       </c>
       <c r="F84">
-        <v>1129.386</v>
+        <v>1143.159</v>
       </c>
       <c r="G84">
         <v>445.8</v>
@@ -8175,37 +8175,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M84">
-        <v>226.7807088</v>
+        <v>229.5463272000001</v>
       </c>
       <c r="N84">
-        <v>-104.0362643555556</v>
+        <v>-106.8018827555557</v>
       </c>
       <c r="O84">
-        <v>-24.96870344533335</v>
+        <v>-25.63245186133335</v>
       </c>
       <c r="P84">
-        <v>-79.06756091022228</v>
+        <v>-81.1694308942223</v>
       </c>
       <c r="Q84">
-        <v>60.63243908977771</v>
+        <v>58.53056910577769</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2237716800034167</v>
+        <v>0.2342406023565589</v>
       </c>
       <c r="T84">
-        <v>2.449847164674182</v>
+        <v>2.593955821419723</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1298993500044421</v>
+        <v>0.12833429759475</v>
       </c>
       <c r="W84">
-        <v>0.174716210519108</v>
+        <v>0.1750304730429742</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5412472916851753</v>
+        <v>0.534726239978125</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1850961950262836</v>
+        <v>0.1866461950262836</v>
       </c>
       <c r="C85">
-        <v>-270.8321255876912</v>
+        <v>-288.0850278489286</v>
       </c>
       <c r="D85">
-        <v>426.5268744123092</v>
+        <v>423.0469721510716</v>
       </c>
       <c r="E85">
-        <v>-38.24099999999976</v>
+        <v>-24.46799999999985</v>
       </c>
       <c r="F85">
-        <v>1143.159</v>
+        <v>1156.932</v>
       </c>
       <c r="G85">
         <v>445.8</v>
@@ -8257,37 +8257,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M85">
-        <v>229.5463272000001</v>
+        <v>232.3119456000001</v>
       </c>
       <c r="N85">
-        <v>-106.8018827555557</v>
+        <v>-109.5675011555556</v>
       </c>
       <c r="O85">
-        <v>-25.63245186133335</v>
+        <v>-26.29620027733336</v>
       </c>
       <c r="P85">
-        <v>-81.1694308942223</v>
+        <v>-83.27130087822229</v>
       </c>
       <c r="Q85">
-        <v>58.53056910577769</v>
+        <v>56.4286991217777</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2342406023565589</v>
+        <v>0.2460181400038438</v>
       </c>
       <c r="T85">
-        <v>2.593955821419723</v>
+        <v>2.756078060258456</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.12833429759475</v>
+        <v>0.1268065083376696</v>
       </c>
       <c r="W85">
-        <v>0.1750304730429742</v>
+        <v>0.175337253125796</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.534726239978125</v>
+        <v>0.5283604514069568</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1866461950262836</v>
+        <v>0.1881961950262836</v>
       </c>
       <c r="C86">
-        <v>-288.0850278489283</v>
+        <v>-305.2816067199096</v>
       </c>
       <c r="D86">
-        <v>423.0469721510717</v>
+        <v>419.6233932800906</v>
       </c>
       <c r="E86">
-        <v>-24.46800000000007</v>
+        <v>-10.69499999999994</v>
       </c>
       <c r="F86">
-        <v>1156.932</v>
+        <v>1170.705</v>
       </c>
       <c r="G86">
         <v>445.8</v>
@@ -8339,37 +8339,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M86">
-        <v>232.3119456</v>
+        <v>235.0775640000001</v>
       </c>
       <c r="N86">
-        <v>-109.5675011555556</v>
+        <v>-112.3331195555556</v>
       </c>
       <c r="O86">
-        <v>-26.29620027733334</v>
+        <v>-26.95994869333335</v>
       </c>
       <c r="P86">
-        <v>-83.27130087822225</v>
+        <v>-85.37317086222228</v>
       </c>
       <c r="Q86">
-        <v>56.42869912177774</v>
+        <v>54.32682913777771</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2460181400038437</v>
+        <v>0.2593660160041</v>
       </c>
       <c r="T86">
-        <v>2.756078060258454</v>
+        <v>2.939816597609018</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1268065083376697</v>
+        <v>0.1253146670631088</v>
       </c>
       <c r="W86">
-        <v>0.1753372531257959</v>
+        <v>0.1756368148537278</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5283604514069569</v>
+        <v>0.5221444460962867</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1881961950262836</v>
+        <v>0.1897461950262836</v>
       </c>
       <c r="C87">
-        <v>-305.2816067199096</v>
+        <v>-322.4232186429606</v>
       </c>
       <c r="D87">
-        <v>419.6233932800906</v>
+        <v>416.2547813570395</v>
       </c>
       <c r="E87">
-        <v>-10.69499999999994</v>
+        <v>3.077999999999975</v>
       </c>
       <c r="F87">
-        <v>1170.705</v>
+        <v>1184.478</v>
       </c>
       <c r="G87">
         <v>445.8</v>
@@ -8421,37 +8421,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M87">
-        <v>235.0775640000001</v>
+        <v>237.8431824</v>
       </c>
       <c r="N87">
-        <v>-112.3331195555556</v>
+        <v>-115.0987379555556</v>
       </c>
       <c r="O87">
-        <v>-26.95994869333335</v>
+        <v>-27.62369710933335</v>
       </c>
       <c r="P87">
-        <v>-85.37317086222228</v>
+        <v>-87.47504084622226</v>
       </c>
       <c r="Q87">
-        <v>54.32682913777771</v>
+        <v>52.22495915377773</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2593660160041</v>
+        <v>0.2746207314329642</v>
       </c>
       <c r="T87">
-        <v>2.939816597609018</v>
+        <v>3.149803497438234</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1253146670631088</v>
+        <v>0.1238575197716773</v>
       </c>
       <c r="W87">
-        <v>0.1756368148537278</v>
+        <v>0.1759294100298472</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5221444460962867</v>
+        <v>0.5160729990486554</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1897461950262836</v>
+        <v>0.1912961950262836</v>
       </c>
       <c r="C88">
-        <v>-322.4232186429606</v>
+        <v>-339.5111768508186</v>
       </c>
       <c r="D88">
-        <v>416.2547813570395</v>
+        <v>412.9398231491816</v>
       </c>
       <c r="E88">
-        <v>3.077999999999975</v>
+        <v>16.85100000000011</v>
       </c>
       <c r="F88">
-        <v>1184.478</v>
+        <v>1198.251</v>
       </c>
       <c r="G88">
         <v>445.8</v>
@@ -8503,37 +8503,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M88">
-        <v>237.8431824</v>
+        <v>240.6088008</v>
       </c>
       <c r="N88">
-        <v>-115.0987379555556</v>
+        <v>-117.8643563555556</v>
       </c>
       <c r="O88">
-        <v>-27.62369710933335</v>
+        <v>-28.28744552533335</v>
       </c>
       <c r="P88">
-        <v>-87.47504084622226</v>
+        <v>-89.57691083022227</v>
       </c>
       <c r="Q88">
-        <v>52.22495915377773</v>
+        <v>50.12308916977771</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2746207314329642</v>
+        <v>0.2922223261585769</v>
       </c>
       <c r="T88">
-        <v>3.149803497438234</v>
+        <v>3.392096074164252</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1238575197716773</v>
+        <v>0.1224338701191293</v>
       </c>
       <c r="W88">
-        <v>0.1759294100298472</v>
+        <v>0.1762152788800788</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5160729990486554</v>
+        <v>0.5101411254963721</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1912961950262836</v>
+        <v>0.1928461950262836</v>
       </c>
       <c r="C89">
-        <v>-339.5111768508186</v>
+        <v>-356.5467530735921</v>
       </c>
       <c r="D89">
-        <v>412.9398231491816</v>
+        <v>409.6772469264081</v>
       </c>
       <c r="E89">
-        <v>16.85100000000011</v>
+        <v>30.62400000000002</v>
       </c>
       <c r="F89">
-        <v>1198.251</v>
+        <v>1212.024</v>
       </c>
       <c r="G89">
         <v>445.8</v>
@@ -8585,37 +8585,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M89">
-        <v>240.6088008</v>
+        <v>243.3744192</v>
       </c>
       <c r="N89">
-        <v>-117.8643563555556</v>
+        <v>-120.6299747555556</v>
       </c>
       <c r="O89">
-        <v>-28.28744552533335</v>
+        <v>-28.95119394133335</v>
       </c>
       <c r="P89">
-        <v>-89.57691083022227</v>
+        <v>-91.67878081422228</v>
       </c>
       <c r="Q89">
-        <v>50.12308916977771</v>
+        <v>48.02121918577771</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2922223261585769</v>
+        <v>0.312757520005125</v>
       </c>
       <c r="T89">
-        <v>3.392096074164252</v>
+        <v>3.674770747011273</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1224338701191293</v>
+        <v>0.1210425761405028</v>
       </c>
       <c r="W89">
-        <v>0.1762152788800788</v>
+        <v>0.176494650710987</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5101411254963721</v>
+        <v>0.5043440672520951</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1928461950262836</v>
+        <v>0.2261130636408255</v>
       </c>
       <c r="C90">
-        <v>-356.5467530735921</v>
+        <v>-429.7173682807465</v>
       </c>
       <c r="D90">
-        <v>409.6772469264081</v>
+        <v>350.2796317192537</v>
       </c>
       <c r="E90">
-        <v>30.62400000000002</v>
+        <v>44.39700000000016</v>
       </c>
       <c r="F90">
-        <v>1212.024</v>
+        <v>1225.797</v>
       </c>
       <c r="G90">
         <v>445.8</v>
@@ -8667,45 +8667,45 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M90">
-        <v>243.3744192</v>
+        <v>289.0429326000001</v>
       </c>
       <c r="N90">
-        <v>-120.6299747555556</v>
+        <v>-166.2984881555557</v>
       </c>
       <c r="O90">
-        <v>-28.95119394133335</v>
+        <v>-39.91163715733336</v>
       </c>
       <c r="P90">
-        <v>-91.67878081422228</v>
+        <v>-126.3868509982223</v>
       </c>
       <c r="Q90">
-        <v>48.02121918577771</v>
+        <v>13.31314900177767</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.312757520005125</v>
+        <v>0.3421797365014265</v>
       </c>
       <c r="T90">
-        <v>3.674770747011273</v>
+        <v>4.079778631751758</v>
       </c>
       <c r="U90">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1210425761405028</v>
+        <v>0.1019179621576627</v>
       </c>
       <c r="W90">
-        <v>0.176494650710987</v>
+        <v>0.2117677445232231</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.5043440672520951</v>
+        <v>0.4246581756569279</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2261130636408255</v>
+        <v>0.2280130636408255</v>
       </c>
       <c r="C91">
-        <v>-429.7173682807465</v>
+        <v>-446.3671191811395</v>
       </c>
       <c r="D91">
-        <v>350.2796317192537</v>
+        <v>347.4028808188606</v>
       </c>
       <c r="E91">
-        <v>44.39700000000016</v>
+        <v>58.17000000000007</v>
       </c>
       <c r="F91">
-        <v>1225.797</v>
+        <v>1239.57</v>
       </c>
       <c r="G91">
         <v>445.8</v>
@@ -8749,37 +8749,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M91">
-        <v>289.0429326000001</v>
+        <v>292.290606</v>
       </c>
       <c r="N91">
-        <v>-166.2984881555557</v>
+        <v>-169.5461615555556</v>
       </c>
       <c r="O91">
-        <v>-39.91163715733336</v>
+        <v>-40.69107877333334</v>
       </c>
       <c r="P91">
-        <v>-126.3868509982223</v>
+        <v>-128.8550827822223</v>
       </c>
       <c r="Q91">
-        <v>13.31314900177767</v>
+        <v>10.84491721777772</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3421797365014265</v>
+        <v>0.3718177101515693</v>
       </c>
       <c r="T91">
-        <v>4.079778631751758</v>
+        <v>4.487756494926935</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1019179621576627</v>
+        <v>0.1007855403559109</v>
       </c>
       <c r="W91">
-        <v>0.2117677445232231</v>
+        <v>0.2120347695840762</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4246581756569279</v>
+        <v>0.4199397514829621</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2280130636408255</v>
+        <v>0.2299130636408255</v>
       </c>
       <c r="C92">
-        <v>-446.3671191811395</v>
+        <v>-462.970003049531</v>
       </c>
       <c r="D92">
-        <v>347.4028808188606</v>
+        <v>344.5729969504692</v>
       </c>
       <c r="E92">
-        <v>58.17000000000007</v>
+        <v>71.94300000000021</v>
       </c>
       <c r="F92">
-        <v>1239.57</v>
+        <v>1253.343</v>
       </c>
       <c r="G92">
         <v>445.8</v>
@@ -8831,37 +8831,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M92">
-        <v>292.290606</v>
+        <v>295.5382794000001</v>
       </c>
       <c r="N92">
-        <v>-169.5461615555556</v>
+        <v>-172.7938349555557</v>
       </c>
       <c r="O92">
-        <v>-40.69107877333334</v>
+        <v>-41.47052038933336</v>
       </c>
       <c r="P92">
-        <v>-128.8550827822223</v>
+        <v>-131.3233145662223</v>
       </c>
       <c r="Q92">
-        <v>10.84491721777772</v>
+        <v>8.376685433777681</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3718177101515693</v>
+        <v>0.4080419001684103</v>
       </c>
       <c r="T92">
-        <v>4.487756494926935</v>
+        <v>4.986396105474372</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1007855403559109</v>
+        <v>0.09967800694540638</v>
       </c>
       <c r="W92">
-        <v>0.2120347695840762</v>
+        <v>0.2122959259622732</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4199397514829621</v>
+        <v>0.4153250289391932</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2299130636408255</v>
+        <v>0.2318130636408255</v>
       </c>
       <c r="C93">
-        <v>-462.970003049531</v>
+        <v>-479.5271559440329</v>
       </c>
       <c r="D93">
-        <v>344.5729969504692</v>
+        <v>341.7888440559673</v>
       </c>
       <c r="E93">
-        <v>71.94300000000021</v>
+        <v>85.71600000000012</v>
       </c>
       <c r="F93">
-        <v>1253.343</v>
+        <v>1267.116</v>
       </c>
       <c r="G93">
         <v>445.8</v>
@@ -8913,37 +8913,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M93">
-        <v>295.5382794000001</v>
+        <v>298.7859528000001</v>
       </c>
       <c r="N93">
-        <v>-172.7938349555557</v>
+        <v>-176.0415083555557</v>
       </c>
       <c r="O93">
-        <v>-41.47052038933336</v>
+        <v>-42.24996200533336</v>
       </c>
       <c r="P93">
-        <v>-131.3233145662223</v>
+        <v>-133.7915463502223</v>
       </c>
       <c r="Q93">
-        <v>8.376685433777681</v>
+        <v>5.908453649777698</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4080419001684103</v>
+        <v>0.4533221376894618</v>
       </c>
       <c r="T93">
-        <v>4.986396105474372</v>
+        <v>5.609695618658671</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09967800694540638</v>
+        <v>0.0985945503481737</v>
       </c>
       <c r="W93">
-        <v>0.2122959259622732</v>
+        <v>0.2125514050279007</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4153250289391932</v>
+        <v>0.4108106264507237</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2318130636408255</v>
+        <v>0.2337130636408255</v>
       </c>
       <c r="C94">
-        <v>-479.5271559440329</v>
+        <v>-496.0396774996178</v>
       </c>
       <c r="D94">
-        <v>341.7888440559673</v>
+        <v>339.0493225003823</v>
       </c>
       <c r="E94">
-        <v>85.71600000000012</v>
+        <v>99.48900000000003</v>
       </c>
       <c r="F94">
-        <v>1267.116</v>
+        <v>1280.889</v>
       </c>
       <c r="G94">
         <v>445.8</v>
@@ -8995,37 +8995,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M94">
-        <v>298.7859528000001</v>
+        <v>302.0336262</v>
       </c>
       <c r="N94">
-        <v>-176.0415083555557</v>
+        <v>-179.2891817555556</v>
       </c>
       <c r="O94">
-        <v>-42.24996200533336</v>
+        <v>-43.02940362133334</v>
       </c>
       <c r="P94">
-        <v>-133.7915463502223</v>
+        <v>-136.2597781342222</v>
       </c>
       <c r="Q94">
-        <v>5.908453649777698</v>
+        <v>3.440221865777744</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4533221376894618</v>
+        <v>0.5115395859308134</v>
       </c>
       <c r="T94">
-        <v>5.609695618658671</v>
+        <v>6.411080707038481</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0985945503481737</v>
+        <v>0.09753439389281701</v>
       </c>
       <c r="W94">
-        <v>0.2125514050279007</v>
+        <v>0.2128013899200737</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4108106264507237</v>
+        <v>0.4063933078867376</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2337130636408255</v>
+        <v>0.2356130636408255</v>
       </c>
       <c r="C95">
-        <v>-496.0396774996178</v>
+        <v>-512.5086323762146</v>
       </c>
       <c r="D95">
-        <v>339.0493225003823</v>
+        <v>336.3533676237857</v>
       </c>
       <c r="E95">
-        <v>99.48900000000003</v>
+        <v>113.2620000000002</v>
       </c>
       <c r="F95">
-        <v>1280.889</v>
+        <v>1294.662</v>
       </c>
       <c r="G95">
         <v>445.8</v>
@@ -9077,37 +9077,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M95">
-        <v>302.0336262</v>
+        <v>305.2812996000001</v>
       </c>
       <c r="N95">
-        <v>-179.2891817555556</v>
+        <v>-182.5368551555557</v>
       </c>
       <c r="O95">
-        <v>-43.02940362133334</v>
+        <v>-43.80884523733336</v>
       </c>
       <c r="P95">
-        <v>-136.2597781342222</v>
+        <v>-138.7280099182223</v>
       </c>
       <c r="Q95">
-        <v>3.440221865777744</v>
+        <v>0.9719900817776761</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5115395859308134</v>
+        <v>0.5891628502526158</v>
       </c>
       <c r="T95">
-        <v>6.411080707038481</v>
+        <v>7.479594158211564</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09753439389281701</v>
+        <v>0.09649679395778703</v>
       </c>
       <c r="W95">
-        <v>0.2128013899200737</v>
+        <v>0.2130460559847538</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4063933078867376</v>
+        <v>0.4020699748241127</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2356130636408255</v>
+        <v>0.2375130636408255</v>
       </c>
       <c r="C96">
-        <v>-512.5086323762146</v>
+        <v>-528.9350516382594</v>
       </c>
       <c r="D96">
-        <v>336.3533676237857</v>
+        <v>333.6999483617407</v>
       </c>
       <c r="E96">
-        <v>113.2620000000002</v>
+        <v>127.0350000000001</v>
       </c>
       <c r="F96">
-        <v>1294.662</v>
+        <v>1308.435</v>
       </c>
       <c r="G96">
         <v>445.8</v>
@@ -9159,37 +9159,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M96">
-        <v>305.2812996000001</v>
+        <v>308.5289730000001</v>
       </c>
       <c r="N96">
-        <v>-182.5368551555557</v>
+        <v>-185.7845285555557</v>
       </c>
       <c r="O96">
-        <v>-43.80884523733336</v>
+        <v>-44.58828685333336</v>
       </c>
       <c r="P96">
-        <v>-138.7280099182223</v>
+        <v>-141.1962417022223</v>
       </c>
       <c r="Q96">
-        <v>0.9719900817776761</v>
+        <v>-1.496241702222306</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5891628502526158</v>
+        <v>0.6978354203031393</v>
       </c>
       <c r="T96">
-        <v>7.479594158211564</v>
+        <v>8.975512989853881</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09649679395778703</v>
+        <v>0.09548103823191559</v>
       </c>
       <c r="W96">
-        <v>0.2130460559847538</v>
+        <v>0.2132855711849143</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4020699748241127</v>
+        <v>0.3978376592996483</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2375130636408255</v>
+        <v>0.2394130636408255</v>
       </c>
       <c r="C97">
-        <v>-528.9350516382594</v>
+        <v>-545.319934069465</v>
       </c>
       <c r="D97">
-        <v>333.6999483617407</v>
+        <v>331.0880659305353</v>
       </c>
       <c r="E97">
-        <v>127.0350000000001</v>
+        <v>140.8080000000002</v>
       </c>
       <c r="F97">
-        <v>1308.435</v>
+        <v>1322.208</v>
       </c>
       <c r="G97">
         <v>445.8</v>
@@ -9241,37 +9241,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M97">
-        <v>308.5289730000001</v>
+        <v>311.7766464000001</v>
       </c>
       <c r="N97">
-        <v>-185.7845285555557</v>
+        <v>-189.0322019555556</v>
       </c>
       <c r="O97">
-        <v>-44.58828685333336</v>
+        <v>-45.36772846933336</v>
       </c>
       <c r="P97">
-        <v>-141.1962417022223</v>
+        <v>-143.6644734862223</v>
       </c>
       <c r="Q97">
-        <v>-1.496241702222306</v>
+        <v>-3.964473486222289</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6978354203031393</v>
+        <v>0.8608442753789245</v>
       </c>
       <c r="T97">
-        <v>8.975512989853881</v>
+        <v>11.21939123731736</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09548103823191559</v>
+        <v>0.09448644408366647</v>
       </c>
       <c r="W97">
-        <v>0.2132855711849143</v>
+        <v>0.2135200964850714</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3978376592996483</v>
+        <v>0.393693517015277</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2394130636408255</v>
+        <v>0.2413130636408255</v>
       </c>
       <c r="C98">
-        <v>-545.3199340694647</v>
+        <v>-561.6642474263183</v>
       </c>
       <c r="D98">
-        <v>331.0880659305354</v>
+        <v>328.5167525736819</v>
       </c>
       <c r="E98">
-        <v>140.808</v>
+        <v>154.5810000000001</v>
       </c>
       <c r="F98">
-        <v>1322.208</v>
+        <v>1335.981</v>
       </c>
       <c r="G98">
         <v>445.8</v>
@@ -9323,37 +9323,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M98">
-        <v>311.7766464</v>
+        <v>315.0243198000001</v>
       </c>
       <c r="N98">
-        <v>-189.0322019555556</v>
+        <v>-192.2798753555556</v>
       </c>
       <c r="O98">
-        <v>-45.36772846933334</v>
+        <v>-46.14717008533335</v>
       </c>
       <c r="P98">
-        <v>-143.6644734862222</v>
+        <v>-146.1327052702223</v>
       </c>
       <c r="Q98">
-        <v>-3.964473486222261</v>
+        <v>-6.4327052702223</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8608442753789222</v>
+        <v>1.13252570050523</v>
       </c>
       <c r="T98">
-        <v>11.21939123731732</v>
+        <v>14.9591883164231</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09448644408366649</v>
+        <v>0.09351235703125754</v>
       </c>
       <c r="W98">
-        <v>0.2135200964850714</v>
+        <v>0.2137497862120295</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.393693517015277</v>
+        <v>0.389634820963573</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2413130636408255</v>
+        <v>0.2432130636408255</v>
       </c>
       <c r="C99">
-        <v>-561.6642474263183</v>
+        <v>-577.9689296336247</v>
       </c>
       <c r="D99">
-        <v>328.5167525736819</v>
+        <v>325.9850703663754</v>
       </c>
       <c r="E99">
-        <v>154.5810000000001</v>
+        <v>168.354</v>
       </c>
       <c r="F99">
-        <v>1335.981</v>
+        <v>1349.754</v>
       </c>
       <c r="G99">
         <v>445.8</v>
@@ -9405,37 +9405,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M99">
-        <v>315.0243198000001</v>
+        <v>318.2719932000001</v>
       </c>
       <c r="N99">
-        <v>-192.2798753555556</v>
+        <v>-195.5275487555556</v>
       </c>
       <c r="O99">
-        <v>-46.14717008533335</v>
+        <v>-46.92661170133335</v>
       </c>
       <c r="P99">
-        <v>-146.1327052702223</v>
+        <v>-148.6009370542223</v>
       </c>
       <c r="Q99">
-        <v>-6.4327052702223</v>
+        <v>-8.900937054222311</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.13252570050523</v>
+        <v>1.675888550757844</v>
       </c>
       <c r="T99">
-        <v>14.9591883164231</v>
+        <v>22.43878247463465</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09351235703125754</v>
+        <v>0.09255814930644879</v>
       </c>
       <c r="W99">
-        <v>0.2137497862120295</v>
+        <v>0.2139747883935394</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.389634820963573</v>
+        <v>0.3856589554435367</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2432130636408255</v>
+        <v>0.2451130636408255</v>
       </c>
       <c r="C100">
-        <v>-577.9689296336247</v>
+        <v>-594.2348899251911</v>
       </c>
       <c r="D100">
-        <v>325.9850703663754</v>
+        <v>323.4921100748092</v>
       </c>
       <c r="E100">
-        <v>168.354</v>
+        <v>182.1270000000002</v>
       </c>
       <c r="F100">
-        <v>1349.754</v>
+        <v>1363.527</v>
       </c>
       <c r="G100">
         <v>445.8</v>
@@ -9487,37 +9487,37 @@
         <v>122.7444444444444</v>
       </c>
       <c r="M100">
-        <v>318.2719932000001</v>
+        <v>321.5196666000001</v>
       </c>
       <c r="N100">
-        <v>-195.5275487555556</v>
+        <v>-198.7752221555556</v>
       </c>
       <c r="O100">
-        <v>-46.92661170133335</v>
+        <v>-47.70605331733335</v>
       </c>
       <c r="P100">
-        <v>-148.6009370542223</v>
+        <v>-151.0691688382223</v>
       </c>
       <c r="Q100">
-        <v>-8.900937054222311</v>
+        <v>-11.36916883822229</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.675888550757844</v>
+        <v>3.305977101515689</v>
       </c>
       <c r="T100">
-        <v>22.43878247463465</v>
+        <v>44.8775649492693</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09255814930644879</v>
+        <v>0.09162321850537355</v>
       </c>
       <c r="W100">
-        <v>0.2139747883935394</v>
+        <v>0.2141952450764329</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3856589554435367</v>
+        <v>0.3817634104390565</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2451130636408255</v>
-      </c>
-      <c r="C101">
-        <v>-594.2348899251911</v>
-      </c>
-      <c r="D101">
-        <v>323.4921100748092</v>
-      </c>
-      <c r="E101">
-        <v>182.1270000000002</v>
-      </c>
-      <c r="F101">
-        <v>1363.527</v>
-      </c>
-      <c r="G101">
-        <v>445.8</v>
-      </c>
-      <c r="H101">
-        <v>195.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>262.4444444444444</v>
-      </c>
-      <c r="K101">
-        <v>139.7</v>
-      </c>
-      <c r="L101">
-        <v>122.7444444444444</v>
-      </c>
-      <c r="M101">
-        <v>321.5196666000001</v>
-      </c>
-      <c r="N101">
-        <v>-198.7752221555556</v>
-      </c>
-      <c r="O101">
-        <v>-47.70605331733335</v>
-      </c>
-      <c r="P101">
-        <v>-151.0691688382223</v>
-      </c>
-      <c r="Q101">
-        <v>-11.36916883822229</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.305977101515689</v>
-      </c>
-      <c r="T101">
-        <v>44.8775649492693</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09162321850537355</v>
-      </c>
-      <c r="W101">
-        <v>0.2141952450764329</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3817634104390565</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
